--- a/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sources &amp; Uses" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Lender Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Stress Tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Revenue Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Staffing &amp; Payroll" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Operating Budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Detailed P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Debt Schedule" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cash Flow &amp; BS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Actuals vs Model" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Uses" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lender Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -98,8 +98,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);&quot;&quot;"/>
     <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
@@ -274,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -370,19 +370,19 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -401,7 +401,7 @@
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -436,7 +436,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,6 +444,24 @@
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3636,11 +3654,11 @@
     <row r="139">
       <c r="A139" s="12" t="inlineStr">
         <is>
-          <t>Opening cash = equity + loan - startup - capex</t>
+          <t>Opening cash = equity + loan - startup - capex - license (paid at close)</t>
         </is>
       </c>
       <c r="B139" s="23">
-        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117</f>
+        <f>Inputs!$B$113+Inputs!$B$110-Inputs!$B$138-Inputs!$B$117-Inputs!$B$120</f>
         <v/>
       </c>
     </row>
@@ -3659,10 +3677,10 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A137:V137"/>
+    <mergeCell ref="A90:V90"/>
     <mergeCell ref="A76:V76"/>
-    <mergeCell ref="A90:V90"/>
-    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A85:V85"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A80:V80"/>
@@ -3672,7 +3690,7 @@
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
     <mergeCell ref="A69:V69"/>
-    <mergeCell ref="A35:V35"/>
+    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
   </mergeCells>
@@ -6023,9 +6041,8 @@
           <t>Hickory license note balance</t>
         </is>
       </c>
-      <c r="B34" s="25">
-        <f>Inputs!$B$120</f>
-        <v/>
+      <c r="B34" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C34" s="25">
         <f>'Debt Schedule'!C22</f>
@@ -6941,7 +6958,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sources &amp; Uses of Financing - Hickory CHOW acquisition + working capital | SBA + seller note + equity</t>
+          <t>Sources &amp; Uses of Financing - Hickory CHOW acquisition + working capital | SBA + equity (seller paid at close)</t>
         </is>
       </c>
     </row>
@@ -6980,12 +6997,11 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Hickory license seller note</t>
-        </is>
-      </c>
-      <c r="B6" s="25">
-        <f>Inputs!$B$120</f>
-        <v/>
+          <t>(Seller paid in full at close - no seller note)</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -7117,7 +7133,7 @@
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, 36 months at 6% seller-financed) - gives Azalea immediate billing capability in San Antonio and an alternative-delivery site serving the East Texas / Tyler market. CHAP/ACHC accreditation transfers with the CHOW; 855A change-of-ownership preserves the provider number with no fresh enrollment delay. The seller note self-finances the license - it shows on both sides above.</t>
+          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, paid in full at close from SBA proceeds and the equity injection - no retained seller note). CHAP/ACHC accreditation transfers with the CHOW; the 855A change-of-ownership preserves the provider number with no fresh enrollment delay. Because the seller is paid at close, the SBA loan is the only debt the business carries.</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7178,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lender Summary - COMBINED debt-service coverage (SBA + Hickory seller note) vs SBA floor 1.25x</t>
+          <t>Lender Summary - SBA-only debt-service coverage (seller paid at close) vs SBA floor 1.25x</t>
         </is>
       </c>
     </row>
@@ -7265,15 +7281,15 @@
           <t>DSCR</t>
         </is>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="62">
         <f>SUM('Operating Budget'!C24:N24)/SUM('Debt Schedule'!C27:N27)</f>
         <v/>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="62">
         <f>SUM('Operating Budget'!O24:R24)/SUM('Debt Schedule'!O27:R27)</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="62">
         <f>SUM('Operating Budget'!S24:V24)/SUM('Debt Schedule'!S27:V27)</f>
         <v/>
       </c>
@@ -7329,7 +7345,7 @@
           <t>Global 3-yr DSCR (target &gt;= 1.25x)</t>
         </is>
       </c>
-      <c r="B14" s="34">
+      <c r="B14" s="63">
         <f>(SUM('Operating Budget'!C24:N24)+SUM('Operating Budget'!O24:R24)+SUM('Operating Budget'!S24:V24))/(SUM('Debt Schedule'!C27:N27)+SUM('Debt Schedule'!O27:R27)+SUM('Debt Schedule'!S27:V27))</f>
         <v/>
       </c>
@@ -7340,7 +7356,7 @@
           <t>Minimum monthly DSCR (Y1)</t>
         </is>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="64">
         <f>MIN('Debt Schedule'!C29:N29)</f>
         <v/>
       </c>
@@ -7370,7 +7386,7 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW (seller-financed at 6% over 36 months), eliminating the 855A enrollment cash gap a fresh startup would face - Azalea bills from day 1 in San Antonio and operates an alternative-delivery site for Tyler/East Texas. The migrated Paloma clinical team brings a proven ~$118K/mo, ~22 ADC book of business. Coverage shown here is COMBINED (SBA + seller note); the seller note retires at month 36, after which DSCR jumps as only the SBA service remains.</t>
+          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW, paid in full at close from SBA proceeds and the equity injection (no retained seller note), eliminating the 855A enrollment cash gap a fresh startup would face. The migrated clinical team brings a proven ~$118K/mo, ~22 ADC book. Because the seller is paid at close, the SBA loan is the only debt - coverage is strong from Year 1 and rises as census builds.</t>
         </is>
       </c>
     </row>
@@ -7681,23 +7697,23 @@
           <t>DSCR</t>
         </is>
       </c>
-      <c r="B17" s="37">
+      <c r="B17" s="65">
         <f>IF(B16=0,0,B15/B16)</f>
         <v/>
       </c>
-      <c r="C17" s="37">
+      <c r="C17" s="65">
         <f>IF(C16=0,0,C15/C16)</f>
         <v/>
       </c>
-      <c r="D17" s="37">
+      <c r="D17" s="65">
         <f>IF(D16=0,0,D15/D16)</f>
         <v/>
       </c>
-      <c r="E17" s="37">
+      <c r="E17" s="65">
         <f>IF(E16=0,0,E15/E16)</f>
         <v/>
       </c>
-      <c r="F17" s="37">
+      <c r="F17" s="65">
         <f>IF(F16=0,0,F15/F16)</f>
         <v/>
       </c>
@@ -8133,83 +8149,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="66">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="66">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="66">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="66">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="66">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="66">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="66">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="66">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="66">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="66">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="44">
+      <c r="M12" s="66">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="44">
+      <c r="N12" s="66">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="44">
+      <c r="O12" s="66">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="66">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="66">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="66">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="44">
+      <c r="S12" s="66">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="44">
+      <c r="T12" s="66">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="44">
+      <c r="U12" s="66">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="44">
+      <c r="V12" s="66">
         <f>V10*V11</f>
         <v/>
       </c>
@@ -18448,7 +18464,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Debt Schedule - SBA 7(a) + Hickory license seller note | Combined DSCR shown (target &gt;= 1.25x)</t>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
         </is>
       </c>
     </row>
@@ -19051,7 +19067,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HICKORY LICENSE SELLER NOTE ($300K, 6%, 36 mo)</t>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
         </is>
       </c>
     </row>
@@ -19061,9 +19077,8 @@
           <t>Beginning balance</t>
         </is>
       </c>
-      <c r="C18" s="25">
-        <f>Inputs!$B$120</f>
-        <v/>
+      <c r="C18" s="25" t="n">
+        <v>0</v>
       </c>
       <c r="D18" s="24">
         <f>C22</f>
@@ -19851,83 +19866,83 @@
           <t>COMBINED DSCR (period)</t>
         </is>
       </c>
-      <c r="C29" s="57">
+      <c r="C29" s="67">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="57">
+      <c r="D29" s="67">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="57">
+      <c r="E29" s="67">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="57">
+      <c r="F29" s="67">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="57">
+      <c r="G29" s="67">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="57">
+      <c r="H29" s="67">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="57">
+      <c r="I29" s="67">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="57">
+      <c r="J29" s="67">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="57">
+      <c r="K29" s="67">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="57">
+      <c r="L29" s="67">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="57">
+      <c r="M29" s="67">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="57">
+      <c r="N29" s="67">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="57">
+      <c r="O29" s="67">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="57">
+      <c r="P29" s="67">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="57">
+      <c r="Q29" s="67">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="57">
+      <c r="R29" s="67">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="57">
+      <c r="S29" s="67">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="57">
+      <c r="T29" s="67">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="57">
+      <c r="U29" s="67">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="57">
+      <c r="V29" s="67">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>

--- a/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -3406,7 +3406,7 @@
         </is>
       </c>
       <c r="B110" s="9" t="n">
-        <v>500000</v>
+        <v>555000</v>
       </c>
     </row>
     <row r="111">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="B113" s="9" t="n">
-        <v>250000</v>
+        <v>195000</v>
       </c>
     </row>
     <row r="114">
@@ -3677,7 +3677,7 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
-    <mergeCell ref="A35:V35"/>
+    <mergeCell ref="A69:V69"/>
     <mergeCell ref="A137:V137"/>
     <mergeCell ref="A90:V90"/>
     <mergeCell ref="A76:V76"/>
@@ -3689,8 +3689,8 @@
     <mergeCell ref="A125:V125"/>
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
-    <mergeCell ref="A69:V69"/>
     <mergeCell ref="A109:V109"/>
+    <mergeCell ref="A35:V35"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
   </mergeCells>

--- a/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -98,8 +98,8 @@
     <numFmt numFmtId="168" formatCode="0.0000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;(#,##0.0);&quot;-&quot;"/>
     <numFmt numFmtId="170" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="171" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
-    <numFmt numFmtId="172" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="172" formatCode="0.00x;(0.00x);&quot;-&quot;"/>
     <numFmt numFmtId="173" formatCode="#,##0.00;(#,##0.00);&quot;&quot;"/>
     <numFmt numFmtId="174" formatCode="#,##0.00;(#,##0.00)"/>
   </numFmts>
@@ -274,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -370,19 +370,19 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="169" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -401,7 +401,7 @@
     <xf numFmtId="169" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -436,7 +436,7 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="172" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -444,24 +444,6 @@
     <xf numFmtId="167" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1227,7 +1209,7 @@
     </comment>
     <comment ref="B110" authorId="0" shapeId="0">
       <text>
-        <t>Sized to fund ramp-period operating need + startup costs. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Sized to pay the seller in full at close + fund startup costs and working-capital reserve. FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B111" authorId="0" shapeId="0">
@@ -1242,7 +1224,7 @@
     </comment>
     <comment ref="B113" authorId="0" shapeId="0">
       <text>
-        <t>FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
+        <t>Cash capital contribution by James Bullard (19.5% passive member). FLAG / CONFIRM: go-forward assumption, not in Paloma actuals.</t>
       </text>
     </comment>
     <comment ref="B114" authorId="0" shapeId="0">
@@ -3677,10 +3659,10 @@
   <mergeCells count="18">
     <mergeCell ref="A2:V2"/>
     <mergeCell ref="A16:V16"/>
-    <mergeCell ref="A69:V69"/>
     <mergeCell ref="A137:V137"/>
+    <mergeCell ref="A76:V76"/>
     <mergeCell ref="A90:V90"/>
-    <mergeCell ref="A76:V76"/>
+    <mergeCell ref="A109:V109"/>
     <mergeCell ref="A85:V85"/>
     <mergeCell ref="A1:V1"/>
     <mergeCell ref="A80:V80"/>
@@ -3689,7 +3671,7 @@
     <mergeCell ref="A125:V125"/>
     <mergeCell ref="A27:V27"/>
     <mergeCell ref="A105:V105"/>
-    <mergeCell ref="A109:V109"/>
+    <mergeCell ref="A69:V69"/>
     <mergeCell ref="A35:V35"/>
     <mergeCell ref="A4:V4"/>
     <mergeCell ref="A24:V24"/>
@@ -6041,8 +6023,9 @@
           <t>Hickory license note balance</t>
         </is>
       </c>
-      <c r="B34" s="25" t="n">
-        <v>0</v>
+      <c r="B34" s="25">
+        <f>0</f>
+        <v/>
       </c>
       <c r="C34" s="25">
         <f>'Debt Schedule'!C22</f>
@@ -6958,7 +6941,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sources &amp; Uses of Financing - Hickory CHOW acquisition + working capital | SBA + equity (seller paid at close)</t>
+          <t>Sources &amp; Uses of Financing - Hickory CHOW (seller paid at close) + working capital | SBA + equity</t>
         </is>
       </c>
     </row>
@@ -6997,11 +6980,12 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>(Seller paid in full at close - no seller note)</t>
-        </is>
-      </c>
-      <c r="B6" s="25" t="n">
-        <v>0</v>
+          <t>Owner equity injection</t>
+        </is>
+      </c>
+      <c r="B6" s="25">
+        <f>Inputs!$B$113</f>
+        <v/>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -7014,13 +6998,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Owner equity injection</t>
-        </is>
-      </c>
-      <c r="B7" s="25">
-        <f>Inputs!$B$113</f>
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL SOURCES</t>
+        </is>
+      </c>
+      <c r="B7" s="27">
+        <f>SUM(B5:B6)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -7034,15 +7018,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL SOURCES</t>
-        </is>
-      </c>
-      <c r="B8" s="27">
-        <f>SUM(B5:B7)</f>
-        <v/>
-      </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>EMR implementation / setup</t>
@@ -7126,14 +7101,14 @@
         </is>
       </c>
       <c r="B16" s="28">
-        <f>B8-D14</f>
+        <f>B7-D14</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="29" t="inlineStr">
         <is>
-          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, paid in full at close from SBA proceeds and the equity injection - no retained seller note). CHAP/ACHC accreditation transfers with the CHOW; the 855A change-of-ownership preserves the provider number with no fresh enrollment delay. Because the seller is paid at close, the SBA loan is the only debt the business carries.</t>
+          <t>CHOW acquisition: Azalea acquires Hickory Hospice's existing Medicare-certified provider number ($300K, paid in full at close from SBA loan + equity proceeds) - gives Azalea immediate billing capability in San Antonio and an alternative-delivery site serving the East Texas / Tyler market. CHAP/ACHC accreditation transfers with the CHOW; 855A change-of-ownership preserves the provider number with no fresh enrollment delay. With no seller note, the SBA loan is the only debt the business carries.</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7153,7 @@
     <row r="2" ht="14" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Lender Summary - SBA-only debt-service coverage (seller paid at close) vs SBA floor 1.25x</t>
+          <t>Lender Summary - SBA 7(a) debt-service coverage (seller paid at close) vs SBA floor 1.25x</t>
         </is>
       </c>
     </row>
@@ -7281,15 +7256,15 @@
           <t>DSCR</t>
         </is>
       </c>
-      <c r="C9" s="62">
+      <c r="C9" s="33">
         <f>SUM('Operating Budget'!C24:N24)/SUM('Debt Schedule'!C27:N27)</f>
         <v/>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="33">
         <f>SUM('Operating Budget'!O24:R24)/SUM('Debt Schedule'!O27:R27)</f>
         <v/>
       </c>
-      <c r="E9" s="62">
+      <c r="E9" s="33">
         <f>SUM('Operating Budget'!S24:V24)/SUM('Debt Schedule'!S27:V27)</f>
         <v/>
       </c>
@@ -7345,7 +7320,7 @@
           <t>Global 3-yr DSCR (target &gt;= 1.25x)</t>
         </is>
       </c>
-      <c r="B14" s="63">
+      <c r="B14" s="34">
         <f>(SUM('Operating Budget'!C24:N24)+SUM('Operating Budget'!O24:R24)+SUM('Operating Budget'!S24:V24))/(SUM('Debt Schedule'!C27:N27)+SUM('Debt Schedule'!O27:R27)+SUM('Debt Schedule'!S27:V27))</f>
         <v/>
       </c>
@@ -7356,7 +7331,7 @@
           <t>Minimum monthly DSCR (Y1)</t>
         </is>
       </c>
-      <c r="B15" s="64">
+      <c r="B15" s="35">
         <f>MIN('Debt Schedule'!C29:N29)</f>
         <v/>
       </c>
@@ -7386,7 +7361,7 @@
     <row r="19">
       <c r="A19" s="29" t="inlineStr">
         <is>
-          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW, paid in full at close from SBA proceeds and the equity injection (no retained seller note), eliminating the 855A enrollment cash gap a fresh startup would face. The migrated clinical team brings a proven ~$118K/mo, ~22 ADC book. Because the seller is paid at close, the SBA loan is the only debt - coverage is strong from Year 1 and rises as census builds.</t>
+          <t>Azalea acquires Hickory Hospice's already-certified Medicare provider number via a $300K CHOW (paid in full at close), eliminating the 855A enrollment cash gap a fresh startup would face - Azalea bills from day 1 in San Antonio and operates an alternative-delivery site for Tyler/East Texas. The migrated Paloma clinical team brings a proven ~$118K/mo, ~22 ADC book of business. With the seller paid at close, the SBA loan is the only debt the business carries, so the coverage shown here is SBA-only - strong from Year 1.</t>
         </is>
       </c>
     </row>
@@ -7697,23 +7672,23 @@
           <t>DSCR</t>
         </is>
       </c>
-      <c r="B17" s="65">
+      <c r="B17" s="37">
         <f>IF(B16=0,0,B15/B16)</f>
         <v/>
       </c>
-      <c r="C17" s="65">
+      <c r="C17" s="37">
         <f>IF(C16=0,0,C15/C16)</f>
         <v/>
       </c>
-      <c r="D17" s="65">
+      <c r="D17" s="37">
         <f>IF(D16=0,0,D15/D16)</f>
         <v/>
       </c>
-      <c r="E17" s="65">
+      <c r="E17" s="37">
         <f>IF(E16=0,0,E15/E16)</f>
         <v/>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="37">
         <f>IF(F16=0,0,F15/F16)</f>
         <v/>
       </c>
@@ -8149,83 +8124,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="66">
+      <c r="C12" s="44">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="66">
+      <c r="D12" s="44">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="66">
+      <c r="E12" s="44">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="44">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="66">
+      <c r="G12" s="44">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="66">
+      <c r="H12" s="44">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="66">
+      <c r="I12" s="44">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="66">
+      <c r="J12" s="44">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="66">
+      <c r="K12" s="44">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="66">
+      <c r="L12" s="44">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="66">
+      <c r="M12" s="44">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="66">
+      <c r="N12" s="44">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="66">
+      <c r="O12" s="44">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="66">
+      <c r="P12" s="44">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="66">
+      <c r="Q12" s="44">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="66">
+      <c r="R12" s="44">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="66">
+      <c r="S12" s="44">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="66">
+      <c r="T12" s="44">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="66">
+      <c r="U12" s="44">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="66">
+      <c r="V12" s="44">
         <f>V10*V11</f>
         <v/>
       </c>
@@ -18493,7 +18468,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>PMT(Inputs!$B$121/12,Inputs!$B$122,-Inputs!$B$120)</f>
+        <f>0</f>
         <v/>
       </c>
     </row>
@@ -19077,8 +19052,9 @@
           <t>Beginning balance</t>
         </is>
       </c>
-      <c r="C18" s="25" t="n">
-        <v>0</v>
+      <c r="C18" s="25">
+        <f>0</f>
+        <v/>
       </c>
       <c r="D18" s="24">
         <f>C22</f>
@@ -19508,7 +19484,7 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>COMBINED DEBT SERVICE &amp; COVERAGE</t>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
         </is>
       </c>
     </row>
@@ -19689,7 +19665,7 @@
     <row r="27">
       <c r="A27" s="26" t="inlineStr">
         <is>
-          <t>TOTAL DEBT SERVICE (P+I, combined)</t>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
         </is>
       </c>
       <c r="C27" s="23">
@@ -19863,86 +19839,86 @@
     <row r="29">
       <c r="A29" s="26" t="inlineStr">
         <is>
-          <t>COMBINED DSCR (period)</t>
-        </is>
-      </c>
-      <c r="C29" s="67">
+          <t>DSCR (period)</t>
+        </is>
+      </c>
+      <c r="C29" s="57">
         <f>IF(C27=0,0,C28/C27)</f>
         <v/>
       </c>
-      <c r="D29" s="67">
+      <c r="D29" s="57">
         <f>IF(D27=0,0,D28/D27)</f>
         <v/>
       </c>
-      <c r="E29" s="67">
+      <c r="E29" s="57">
         <f>IF(E27=0,0,E28/E27)</f>
         <v/>
       </c>
-      <c r="F29" s="67">
+      <c r="F29" s="57">
         <f>IF(F27=0,0,F28/F27)</f>
         <v/>
       </c>
-      <c r="G29" s="67">
+      <c r="G29" s="57">
         <f>IF(G27=0,0,G28/G27)</f>
         <v/>
       </c>
-      <c r="H29" s="67">
+      <c r="H29" s="57">
         <f>IF(H27=0,0,H28/H27)</f>
         <v/>
       </c>
-      <c r="I29" s="67">
+      <c r="I29" s="57">
         <f>IF(I27=0,0,I28/I27)</f>
         <v/>
       </c>
-      <c r="J29" s="67">
+      <c r="J29" s="57">
         <f>IF(J27=0,0,J28/J27)</f>
         <v/>
       </c>
-      <c r="K29" s="67">
+      <c r="K29" s="57">
         <f>IF(K27=0,0,K28/K27)</f>
         <v/>
       </c>
-      <c r="L29" s="67">
+      <c r="L29" s="57">
         <f>IF(L27=0,0,L28/L27)</f>
         <v/>
       </c>
-      <c r="M29" s="67">
+      <c r="M29" s="57">
         <f>IF(M27=0,0,M28/M27)</f>
         <v/>
       </c>
-      <c r="N29" s="67">
+      <c r="N29" s="57">
         <f>IF(N27=0,0,N28/N27)</f>
         <v/>
       </c>
-      <c r="O29" s="67">
+      <c r="O29" s="57">
         <f>IF(O27=0,0,O28/O27)</f>
         <v/>
       </c>
-      <c r="P29" s="67">
+      <c r="P29" s="57">
         <f>IF(P27=0,0,P28/P27)</f>
         <v/>
       </c>
-      <c r="Q29" s="67">
+      <c r="Q29" s="57">
         <f>IF(Q27=0,0,Q28/Q27)</f>
         <v/>
       </c>
-      <c r="R29" s="67">
+      <c r="R29" s="57">
         <f>IF(R27=0,0,R28/R27)</f>
         <v/>
       </c>
-      <c r="S29" s="67">
+      <c r="S29" s="57">
         <f>IF(S27=0,0,S28/S27)</f>
         <v/>
       </c>
-      <c r="T29" s="67">
+      <c r="T29" s="57">
         <f>IF(T27=0,0,T28/T27)</f>
         <v/>
       </c>
-      <c r="U29" s="67">
+      <c r="U29" s="57">
         <f>IF(U27=0,0,U28/U27)</f>
         <v/>
       </c>
-      <c r="V29" s="67">
+      <c r="V29" s="57">
         <f>IF(V27=0,0,V28/V27)</f>
         <v/>
       </c>

--- a/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
+++ b/sba_application/09_financial_model/Azalea_Hospice_SBA_Loan_Package.xlsx
@@ -11,13 +11,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Uses" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lender Summary" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MVI Upside" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Staffing &amp; Payroll" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Budget" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detailed P&amp;L" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow &amp; BS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actuals vs Model" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="rhc_tier1">Inputs!$B$5</definedName>
@@ -388,6 +389,9 @@
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -405,9 +409,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1349,6 +1350,21 @@
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
       <text>
+        <t>Sustained incremental census from MVI 'Perfect Visit' certification + the national campaign. Illustrative only - not used for underwriting.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Azalea Hospice</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
         <t>Source: Paloma P&amp;L 2025.</t>
       </text>
     </comment>
@@ -3688,6 +3704,1550 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:V29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="11" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="11" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>LOAN TERMS (from Inputs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>SBA monthly payment (PMT)</t>
+        </is>
+      </c>
+      <c r="B5" s="24">
+        <f>PMT(Inputs!$B$111/12,Inputs!$B$112,-Inputs!$B$110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>License note monthly payment (PMT)</t>
+        </is>
+      </c>
+      <c r="B6" s="24">
+        <f>0</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>($ per period)</t>
+        </is>
+      </c>
+      <c r="C8" s="42" t="inlineStr">
+        <is>
+          <t>YEAR 1 - monthly</t>
+        </is>
+      </c>
+      <c r="O8" s="42" t="inlineStr">
+        <is>
+          <t>YEAR 2 - quarterly</t>
+        </is>
+      </c>
+      <c r="S8" s="42" t="inlineStr">
+        <is>
+          <t>YEAR 3 - quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr"/>
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="D9" s="30" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="E9" s="30" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="F9" s="30" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="G9" s="30" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="H9" s="30" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="I9" s="30" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="J9" s="30" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="K9" s="30" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="L9" s="30" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="M9" s="30" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="N9" s="30" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="O9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q1</t>
+        </is>
+      </c>
+      <c r="P9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q2</t>
+        </is>
+      </c>
+      <c r="Q9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q3</t>
+        </is>
+      </c>
+      <c r="R9" s="30" t="inlineStr">
+        <is>
+          <t>Y2 Q4</t>
+        </is>
+      </c>
+      <c r="S9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q1</t>
+        </is>
+      </c>
+      <c r="T9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q2</t>
+        </is>
+      </c>
+      <c r="U9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q3</t>
+        </is>
+      </c>
+      <c r="V9" s="30" t="inlineStr">
+        <is>
+          <t>Y3 Q4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>SBA 7(a) LOAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Beginning balance</t>
+        </is>
+      </c>
+      <c r="C11" s="25">
+        <f>Inputs!$B$110</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>D15</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>E15</f>
+        <v/>
+      </c>
+      <c r="G11" s="24">
+        <f>F15</f>
+        <v/>
+      </c>
+      <c r="H11" s="24">
+        <f>G15</f>
+        <v/>
+      </c>
+      <c r="I11" s="24">
+        <f>H15</f>
+        <v/>
+      </c>
+      <c r="J11" s="24">
+        <f>I15</f>
+        <v/>
+      </c>
+      <c r="K11" s="24">
+        <f>J15</f>
+        <v/>
+      </c>
+      <c r="L11" s="24">
+        <f>K15</f>
+        <v/>
+      </c>
+      <c r="M11" s="24">
+        <f>L15</f>
+        <v/>
+      </c>
+      <c r="N11" s="24">
+        <f>M15</f>
+        <v/>
+      </c>
+      <c r="O11" s="24">
+        <f>N15</f>
+        <v/>
+      </c>
+      <c r="P11" s="24">
+        <f>O15</f>
+        <v/>
+      </c>
+      <c r="Q11" s="24">
+        <f>P15</f>
+        <v/>
+      </c>
+      <c r="R11" s="24">
+        <f>Q15</f>
+        <v/>
+      </c>
+      <c r="S11" s="24">
+        <f>R15</f>
+        <v/>
+      </c>
+      <c r="T11" s="24">
+        <f>S15</f>
+        <v/>
+      </c>
+      <c r="U11" s="24">
+        <f>T15</f>
+        <v/>
+      </c>
+      <c r="V11" s="24">
+        <f>U15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+      <c r="C12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="G12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="H12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="I12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="J12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="K12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="L12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="M12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="N12" s="24">
+        <f>'Debt Schedule'!$B$5*1</f>
+        <v/>
+      </c>
+      <c r="O12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="P12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="Q12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="R12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="S12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="T12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="U12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+      <c r="V12" s="24">
+        <f>'Debt Schedule'!$B$5*3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C13" s="24">
+        <f>C11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>D11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>E11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="F13" s="24">
+        <f>F11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="G13" s="24">
+        <f>G11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="H13" s="24">
+        <f>H11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="I13" s="24">
+        <f>I11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="J13" s="24">
+        <f>J11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="K13" s="24">
+        <f>K11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="L13" s="24">
+        <f>L11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="M13" s="24">
+        <f>M11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="N13" s="24">
+        <f>N11*Inputs!$B$111/12*1</f>
+        <v/>
+      </c>
+      <c r="O13" s="24">
+        <f>O11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="P13" s="24">
+        <f>P11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="Q13" s="24">
+        <f>Q11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="R13" s="24">
+        <f>R11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="S13" s="24">
+        <f>S11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="T13" s="24">
+        <f>T11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="U13" s="24">
+        <f>U11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+      <c r="V13" s="24">
+        <f>V11*Inputs!$B$111/12*3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C14" s="24">
+        <f>C12-C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D12-D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>E12-E13</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>F12-F13</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>G12-G13</f>
+        <v/>
+      </c>
+      <c r="H14" s="24">
+        <f>H12-H13</f>
+        <v/>
+      </c>
+      <c r="I14" s="24">
+        <f>I12-I13</f>
+        <v/>
+      </c>
+      <c r="J14" s="24">
+        <f>J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="24">
+        <f>K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="24">
+        <f>L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="24">
+        <f>M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="24">
+        <f>N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="24">
+        <f>O12-O13</f>
+        <v/>
+      </c>
+      <c r="P14" s="24">
+        <f>P12-P13</f>
+        <v/>
+      </c>
+      <c r="Q14" s="24">
+        <f>Q12-Q13</f>
+        <v/>
+      </c>
+      <c r="R14" s="24">
+        <f>R12-R13</f>
+        <v/>
+      </c>
+      <c r="S14" s="24">
+        <f>S12-S13</f>
+        <v/>
+      </c>
+      <c r="T14" s="24">
+        <f>T12-T13</f>
+        <v/>
+      </c>
+      <c r="U14" s="24">
+        <f>U12-U13</f>
+        <v/>
+      </c>
+      <c r="V14" s="24">
+        <f>V12-V13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>Ending balance</t>
+        </is>
+      </c>
+      <c r="C15" s="23">
+        <f>C11-C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="23">
+        <f>D11-D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="23">
+        <f>E11-E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="23">
+        <f>F11-F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="23">
+        <f>G11-G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="23">
+        <f>H11-H14</f>
+        <v/>
+      </c>
+      <c r="I15" s="23">
+        <f>I11-I14</f>
+        <v/>
+      </c>
+      <c r="J15" s="23">
+        <f>J11-J14</f>
+        <v/>
+      </c>
+      <c r="K15" s="23">
+        <f>K11-K14</f>
+        <v/>
+      </c>
+      <c r="L15" s="23">
+        <f>L11-L14</f>
+        <v/>
+      </c>
+      <c r="M15" s="23">
+        <f>M11-M14</f>
+        <v/>
+      </c>
+      <c r="N15" s="23">
+        <f>N11-N14</f>
+        <v/>
+      </c>
+      <c r="O15" s="23">
+        <f>O11-O14</f>
+        <v/>
+      </c>
+      <c r="P15" s="23">
+        <f>P11-P14</f>
+        <v/>
+      </c>
+      <c r="Q15" s="23">
+        <f>Q11-Q14</f>
+        <v/>
+      </c>
+      <c r="R15" s="23">
+        <f>R11-R14</f>
+        <v/>
+      </c>
+      <c r="S15" s="23">
+        <f>S11-S14</f>
+        <v/>
+      </c>
+      <c r="T15" s="23">
+        <f>T11-T14</f>
+        <v/>
+      </c>
+      <c r="U15" s="23">
+        <f>U11-U14</f>
+        <v/>
+      </c>
+      <c r="V15" s="23">
+        <f>V11-V14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Beginning balance</t>
+        </is>
+      </c>
+      <c r="C18" s="25">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>D22</f>
+        <v/>
+      </c>
+      <c r="F18" s="24">
+        <f>E22</f>
+        <v/>
+      </c>
+      <c r="G18" s="24">
+        <f>F22</f>
+        <v/>
+      </c>
+      <c r="H18" s="24">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="I18" s="24">
+        <f>H22</f>
+        <v/>
+      </c>
+      <c r="J18" s="24">
+        <f>I22</f>
+        <v/>
+      </c>
+      <c r="K18" s="24">
+        <f>J22</f>
+        <v/>
+      </c>
+      <c r="L18" s="24">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="M18" s="24">
+        <f>L22</f>
+        <v/>
+      </c>
+      <c r="N18" s="24">
+        <f>M22</f>
+        <v/>
+      </c>
+      <c r="O18" s="24">
+        <f>N22</f>
+        <v/>
+      </c>
+      <c r="P18" s="24">
+        <f>O22</f>
+        <v/>
+      </c>
+      <c r="Q18" s="24">
+        <f>P22</f>
+        <v/>
+      </c>
+      <c r="R18" s="24">
+        <f>Q22</f>
+        <v/>
+      </c>
+      <c r="S18" s="24">
+        <f>R22</f>
+        <v/>
+      </c>
+      <c r="T18" s="24">
+        <f>S22</f>
+        <v/>
+      </c>
+      <c r="U18" s="24">
+        <f>T22</f>
+        <v/>
+      </c>
+      <c r="V18" s="24">
+        <f>U22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Ending balance (closed-form)</t>
+        </is>
+      </c>
+      <c r="C19" s="24">
+        <f>MAX(0,C18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>MAX(0,D18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>MAX(0,E18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="F19" s="24">
+        <f>MAX(0,F18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="G19" s="24">
+        <f>MAX(0,G18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="H19" s="24">
+        <f>MAX(0,H18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="I19" s="24">
+        <f>MAX(0,I18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="J19" s="24">
+        <f>MAX(0,J18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="K19" s="24">
+        <f>MAX(0,K18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="L19" s="24">
+        <f>MAX(0,L18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="M19" s="24">
+        <f>MAX(0,M18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="N19" s="24">
+        <f>MAX(0,N18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="O19" s="24">
+        <f>MAX(0,O18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="P19" s="24">
+        <f>MAX(0,P18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="24">
+        <f>MAX(0,Q18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="R19" s="24">
+        <f>MAX(0,R18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="S19" s="24">
+        <f>MAX(0,S18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="T19" s="24">
+        <f>MAX(0,T18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="U19" s="24">
+        <f>MAX(0,U18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+      <c r="V19" s="24">
+        <f>MAX(0,V18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Principal</t>
+        </is>
+      </c>
+      <c r="C20" s="24">
+        <f>C18-C19</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>D18-D19</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>E18-E19</f>
+        <v/>
+      </c>
+      <c r="F20" s="24">
+        <f>F18-F19</f>
+        <v/>
+      </c>
+      <c r="G20" s="24">
+        <f>G18-G19</f>
+        <v/>
+      </c>
+      <c r="H20" s="24">
+        <f>H18-H19</f>
+        <v/>
+      </c>
+      <c r="I20" s="24">
+        <f>I18-I19</f>
+        <v/>
+      </c>
+      <c r="J20" s="24">
+        <f>J18-J19</f>
+        <v/>
+      </c>
+      <c r="K20" s="24">
+        <f>K18-K19</f>
+        <v/>
+      </c>
+      <c r="L20" s="24">
+        <f>L18-L19</f>
+        <v/>
+      </c>
+      <c r="M20" s="24">
+        <f>M18-M19</f>
+        <v/>
+      </c>
+      <c r="N20" s="24">
+        <f>N18-N19</f>
+        <v/>
+      </c>
+      <c r="O20" s="24">
+        <f>O18-O19</f>
+        <v/>
+      </c>
+      <c r="P20" s="24">
+        <f>P18-P19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="24">
+        <f>Q18-Q19</f>
+        <v/>
+      </c>
+      <c r="R20" s="24">
+        <f>R18-R19</f>
+        <v/>
+      </c>
+      <c r="S20" s="24">
+        <f>S18-S19</f>
+        <v/>
+      </c>
+      <c r="T20" s="24">
+        <f>T18-T19</f>
+        <v/>
+      </c>
+      <c r="U20" s="24">
+        <f>U18-U19</f>
+        <v/>
+      </c>
+      <c r="V20" s="24">
+        <f>V18-V19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="C21" s="24">
+        <f>MAX(0,IF(C18=0,0,'Debt Schedule'!$B$6*1-C20))</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>MAX(0,IF(D18=0,0,'Debt Schedule'!$B$6*1-D20))</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>MAX(0,IF(E18=0,0,'Debt Schedule'!$B$6*1-E20))</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>MAX(0,IF(F18=0,0,'Debt Schedule'!$B$6*1-F20))</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>MAX(0,IF(G18=0,0,'Debt Schedule'!$B$6*1-G20))</f>
+        <v/>
+      </c>
+      <c r="H21" s="24">
+        <f>MAX(0,IF(H18=0,0,'Debt Schedule'!$B$6*1-H20))</f>
+        <v/>
+      </c>
+      <c r="I21" s="24">
+        <f>MAX(0,IF(I18=0,0,'Debt Schedule'!$B$6*1-I20))</f>
+        <v/>
+      </c>
+      <c r="J21" s="24">
+        <f>MAX(0,IF(J18=0,0,'Debt Schedule'!$B$6*1-J20))</f>
+        <v/>
+      </c>
+      <c r="K21" s="24">
+        <f>MAX(0,IF(K18=0,0,'Debt Schedule'!$B$6*1-K20))</f>
+        <v/>
+      </c>
+      <c r="L21" s="24">
+        <f>MAX(0,IF(L18=0,0,'Debt Schedule'!$B$6*1-L20))</f>
+        <v/>
+      </c>
+      <c r="M21" s="24">
+        <f>MAX(0,IF(M18=0,0,'Debt Schedule'!$B$6*1-M20))</f>
+        <v/>
+      </c>
+      <c r="N21" s="24">
+        <f>MAX(0,IF(N18=0,0,'Debt Schedule'!$B$6*1-N20))</f>
+        <v/>
+      </c>
+      <c r="O21" s="24">
+        <f>MAX(0,IF(O18=0,0,'Debt Schedule'!$B$6*3-O20))</f>
+        <v/>
+      </c>
+      <c r="P21" s="24">
+        <f>MAX(0,IF(P18=0,0,'Debt Schedule'!$B$6*3-P20))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="24">
+        <f>MAX(0,IF(Q18=0,0,'Debt Schedule'!$B$6*3-Q20))</f>
+        <v/>
+      </c>
+      <c r="R21" s="24">
+        <f>MAX(0,IF(R18=0,0,'Debt Schedule'!$B$6*3-R20))</f>
+        <v/>
+      </c>
+      <c r="S21" s="24">
+        <f>MAX(0,IF(S18=0,0,'Debt Schedule'!$B$6*3-S20))</f>
+        <v/>
+      </c>
+      <c r="T21" s="24">
+        <f>MAX(0,IF(T18=0,0,'Debt Schedule'!$B$6*3-T20))</f>
+        <v/>
+      </c>
+      <c r="U21" s="24">
+        <f>MAX(0,IF(U18=0,0,'Debt Schedule'!$B$6*3-U20))</f>
+        <v/>
+      </c>
+      <c r="V21" s="24">
+        <f>MAX(0,IF(V18=0,0,'Debt Schedule'!$B$6*3-V20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Ending balance</t>
+        </is>
+      </c>
+      <c r="C22" s="23">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="D22" s="23">
+        <f>D19</f>
+        <v/>
+      </c>
+      <c r="E22" s="23">
+        <f>E19</f>
+        <v/>
+      </c>
+      <c r="F22" s="23">
+        <f>F19</f>
+        <v/>
+      </c>
+      <c r="G22" s="23">
+        <f>G19</f>
+        <v/>
+      </c>
+      <c r="H22" s="23">
+        <f>H19</f>
+        <v/>
+      </c>
+      <c r="I22" s="23">
+        <f>I19</f>
+        <v/>
+      </c>
+      <c r="J22" s="23">
+        <f>J19</f>
+        <v/>
+      </c>
+      <c r="K22" s="23">
+        <f>K19</f>
+        <v/>
+      </c>
+      <c r="L22" s="23">
+        <f>L19</f>
+        <v/>
+      </c>
+      <c r="M22" s="23">
+        <f>M19</f>
+        <v/>
+      </c>
+      <c r="N22" s="23">
+        <f>N19</f>
+        <v/>
+      </c>
+      <c r="O22" s="23">
+        <f>O19</f>
+        <v/>
+      </c>
+      <c r="P22" s="23">
+        <f>P19</f>
+        <v/>
+      </c>
+      <c r="Q22" s="23">
+        <f>Q19</f>
+        <v/>
+      </c>
+      <c r="R22" s="23">
+        <f>R19</f>
+        <v/>
+      </c>
+      <c r="S22" s="23">
+        <f>S19</f>
+        <v/>
+      </c>
+      <c r="T22" s="23">
+        <f>T19</f>
+        <v/>
+      </c>
+      <c r="U22" s="23">
+        <f>U19</f>
+        <v/>
+      </c>
+      <c r="V22" s="23">
+        <f>V19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Total interest</t>
+        </is>
+      </c>
+      <c r="C25" s="24">
+        <f>C13+C21</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>D13+D21</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>E13+E21</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>F13+F21</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>G13+G21</f>
+        <v/>
+      </c>
+      <c r="H25" s="24">
+        <f>H13+H21</f>
+        <v/>
+      </c>
+      <c r="I25" s="24">
+        <f>I13+I21</f>
+        <v/>
+      </c>
+      <c r="J25" s="24">
+        <f>J13+J21</f>
+        <v/>
+      </c>
+      <c r="K25" s="24">
+        <f>K13+K21</f>
+        <v/>
+      </c>
+      <c r="L25" s="24">
+        <f>L13+L21</f>
+        <v/>
+      </c>
+      <c r="M25" s="24">
+        <f>M13+M21</f>
+        <v/>
+      </c>
+      <c r="N25" s="24">
+        <f>N13+N21</f>
+        <v/>
+      </c>
+      <c r="O25" s="24">
+        <f>O13+O21</f>
+        <v/>
+      </c>
+      <c r="P25" s="24">
+        <f>P13+P21</f>
+        <v/>
+      </c>
+      <c r="Q25" s="24">
+        <f>Q13+Q21</f>
+        <v/>
+      </c>
+      <c r="R25" s="24">
+        <f>R13+R21</f>
+        <v/>
+      </c>
+      <c r="S25" s="24">
+        <f>S13+S21</f>
+        <v/>
+      </c>
+      <c r="T25" s="24">
+        <f>T13+T21</f>
+        <v/>
+      </c>
+      <c r="U25" s="24">
+        <f>U13+U21</f>
+        <v/>
+      </c>
+      <c r="V25" s="24">
+        <f>V13+V21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Total principal</t>
+        </is>
+      </c>
+      <c r="C26" s="24">
+        <f>C14+C20</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>D14+D20</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>E14+E20</f>
+        <v/>
+      </c>
+      <c r="F26" s="24">
+        <f>F14+F20</f>
+        <v/>
+      </c>
+      <c r="G26" s="24">
+        <f>G14+G20</f>
+        <v/>
+      </c>
+      <c r="H26" s="24">
+        <f>H14+H20</f>
+        <v/>
+      </c>
+      <c r="I26" s="24">
+        <f>I14+I20</f>
+        <v/>
+      </c>
+      <c r="J26" s="24">
+        <f>J14+J20</f>
+        <v/>
+      </c>
+      <c r="K26" s="24">
+        <f>K14+K20</f>
+        <v/>
+      </c>
+      <c r="L26" s="24">
+        <f>L14+L20</f>
+        <v/>
+      </c>
+      <c r="M26" s="24">
+        <f>M14+M20</f>
+        <v/>
+      </c>
+      <c r="N26" s="24">
+        <f>N14+N20</f>
+        <v/>
+      </c>
+      <c r="O26" s="24">
+        <f>O14+O20</f>
+        <v/>
+      </c>
+      <c r="P26" s="24">
+        <f>P14+P20</f>
+        <v/>
+      </c>
+      <c r="Q26" s="24">
+        <f>Q14+Q20</f>
+        <v/>
+      </c>
+      <c r="R26" s="24">
+        <f>R14+R20</f>
+        <v/>
+      </c>
+      <c r="S26" s="24">
+        <f>S14+S20</f>
+        <v/>
+      </c>
+      <c r="T26" s="24">
+        <f>T14+T20</f>
+        <v/>
+      </c>
+      <c r="U26" s="24">
+        <f>U14+U20</f>
+        <v/>
+      </c>
+      <c r="V26" s="24">
+        <f>V14+V20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="inlineStr">
+        <is>
+          <t>TOTAL DEBT SERVICE (P+I)</t>
+        </is>
+      </c>
+      <c r="C27" s="23">
+        <f>C25+C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="23">
+        <f>D25+D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="23">
+        <f>E25+E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="23">
+        <f>F25+F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="23">
+        <f>G25+G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="23">
+        <f>H25+H26</f>
+        <v/>
+      </c>
+      <c r="I27" s="23">
+        <f>I25+I26</f>
+        <v/>
+      </c>
+      <c r="J27" s="23">
+        <f>J25+J26</f>
+        <v/>
+      </c>
+      <c r="K27" s="23">
+        <f>K25+K26</f>
+        <v/>
+      </c>
+      <c r="L27" s="23">
+        <f>L25+L26</f>
+        <v/>
+      </c>
+      <c r="M27" s="23">
+        <f>M25+M26</f>
+        <v/>
+      </c>
+      <c r="N27" s="23">
+        <f>N25+N26</f>
+        <v/>
+      </c>
+      <c r="O27" s="23">
+        <f>O25+O26</f>
+        <v/>
+      </c>
+      <c r="P27" s="23">
+        <f>P25+P26</f>
+        <v/>
+      </c>
+      <c r="Q27" s="23">
+        <f>Q25+Q26</f>
+        <v/>
+      </c>
+      <c r="R27" s="23">
+        <f>R25+R26</f>
+        <v/>
+      </c>
+      <c r="S27" s="23">
+        <f>S25+S26</f>
+        <v/>
+      </c>
+      <c r="T27" s="23">
+        <f>T25+T26</f>
+        <v/>
+      </c>
+      <c r="U27" s="23">
+        <f>U25+U26</f>
+        <v/>
+      </c>
+      <c r="V27" s="23">
+        <f>V25+V26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>EBITDA (link)</t>
+        </is>
+      </c>
+      <c r="C28" s="25">
+        <f>'Operating Budget'!C24</f>
+        <v/>
+      </c>
+      <c r="D28" s="25">
+        <f>'Operating Budget'!D24</f>
+        <v/>
+      </c>
+      <c r="E28" s="25">
+        <f>'Operating Budget'!E24</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>'Operating Budget'!F24</f>
+        <v/>
+      </c>
+      <c r="G28" s="25">
+        <f>'Operating Budget'!G24</f>
+        <v/>
+      </c>
+      <c r="H28" s="25">
+        <f>'Operating Budget'!H24</f>
+        <v/>
+      </c>
+      <c r="I28" s="25">
+        <f>'Operating Budget'!I24</f>
+        <v/>
+      </c>
+      <c r="J28" s="25">
+        <f>'Operating Budget'!J24</f>
+        <v/>
+      </c>
+      <c r="K28" s="25">
+        <f>'Operating Budget'!K24</f>
+        <v/>
+      </c>
+      <c r="L28" s="25">
+        <f>'Operating Budget'!L24</f>
+        <v/>
+      </c>
+      <c r="M28" s="25">
+        <f>'Operating Budget'!M24</f>
+        <v/>
+      </c>
+      <c r="N28" s="25">
+        <f>'Operating Budget'!N24</f>
+        <v/>
+      </c>
+      <c r="O28" s="25">
+        <f>'Operating Budget'!O24</f>
+        <v/>
+      </c>
+      <c r="P28" s="25">
+        <f>'Operating Budget'!P24</f>
+        <v/>
+      </c>
+      <c r="Q28" s="25">
+        <f>'Operating Budget'!Q24</f>
+        <v/>
+      </c>
+      <c r="R28" s="25">
+        <f>'Operating Budget'!R24</f>
+        <v/>
+      </c>
+      <c r="S28" s="25">
+        <f>'Operating Budget'!S24</f>
+        <v/>
+      </c>
+      <c r="T28" s="25">
+        <f>'Operating Budget'!T24</f>
+        <v/>
+      </c>
+      <c r="U28" s="25">
+        <f>'Operating Budget'!U24</f>
+        <v/>
+      </c>
+      <c r="V28" s="25">
+        <f>'Operating Budget'!V24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="26" t="inlineStr">
+        <is>
+          <t>DSCR (period)</t>
+        </is>
+      </c>
+      <c r="C29" s="57">
+        <f>IF(C27=0,0,C28/C27)</f>
+        <v/>
+      </c>
+      <c r="D29" s="57">
+        <f>IF(D27=0,0,D28/D27)</f>
+        <v/>
+      </c>
+      <c r="E29" s="57">
+        <f>IF(E27=0,0,E28/E27)</f>
+        <v/>
+      </c>
+      <c r="F29" s="57">
+        <f>IF(F27=0,0,F28/F27)</f>
+        <v/>
+      </c>
+      <c r="G29" s="57">
+        <f>IF(G27=0,0,G28/G27)</f>
+        <v/>
+      </c>
+      <c r="H29" s="57">
+        <f>IF(H27=0,0,H28/H27)</f>
+        <v/>
+      </c>
+      <c r="I29" s="57">
+        <f>IF(I27=0,0,I28/I27)</f>
+        <v/>
+      </c>
+      <c r="J29" s="57">
+        <f>IF(J27=0,0,J28/J27)</f>
+        <v/>
+      </c>
+      <c r="K29" s="57">
+        <f>IF(K27=0,0,K28/K27)</f>
+        <v/>
+      </c>
+      <c r="L29" s="57">
+        <f>IF(L27=0,0,L28/L27)</f>
+        <v/>
+      </c>
+      <c r="M29" s="57">
+        <f>IF(M27=0,0,M28/M27)</f>
+        <v/>
+      </c>
+      <c r="N29" s="57">
+        <f>IF(N27=0,0,N28/N27)</f>
+        <v/>
+      </c>
+      <c r="O29" s="57">
+        <f>IF(O27=0,0,O28/O27)</f>
+        <v/>
+      </c>
+      <c r="P29" s="57">
+        <f>IF(P27=0,0,P28/P27)</f>
+        <v/>
+      </c>
+      <c r="Q29" s="57">
+        <f>IF(Q27=0,0,Q28/Q27)</f>
+        <v/>
+      </c>
+      <c r="R29" s="57">
+        <f>IF(R27=0,0,R28/R27)</f>
+        <v/>
+      </c>
+      <c r="S29" s="57">
+        <f>IF(S27=0,0,S28/S27)</f>
+        <v/>
+      </c>
+      <c r="T29" s="57">
+        <f>IF(T27=0,0,T28/T27)</f>
+        <v/>
+      </c>
+      <c r="U29" s="57">
+        <f>IF(U27=0,0,U28/U27)</f>
+        <v/>
+      </c>
+      <c r="V29" s="57">
+        <f>IF(V27=0,0,V28/V27)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A10:V10"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="A17:V17"/>
+    <mergeCell ref="C8:N8"/>
+    <mergeCell ref="A4:V4"/>
+    <mergeCell ref="A24:V24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00808080"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3730,34 +5290,34 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>Opening</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="41" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="41" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr"/>
+      <c r="A5" s="43" t="inlineStr"/>
       <c r="C5" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -5110,83 +6670,83 @@
           <t>ENDING CASH</t>
         </is>
       </c>
-      <c r="C21" s="45">
+      <c r="C21" s="46">
         <f>C18+C19</f>
         <v/>
       </c>
-      <c r="D21" s="45">
+      <c r="D21" s="46">
         <f>D18+D19</f>
         <v/>
       </c>
-      <c r="E21" s="45">
+      <c r="E21" s="46">
         <f>E18+E19</f>
         <v/>
       </c>
-      <c r="F21" s="45">
+      <c r="F21" s="46">
         <f>F18+F19</f>
         <v/>
       </c>
-      <c r="G21" s="45">
+      <c r="G21" s="46">
         <f>G18+G19</f>
         <v/>
       </c>
-      <c r="H21" s="45">
+      <c r="H21" s="46">
         <f>H18+H19</f>
         <v/>
       </c>
-      <c r="I21" s="45">
+      <c r="I21" s="46">
         <f>I18+I19</f>
         <v/>
       </c>
-      <c r="J21" s="45">
+      <c r="J21" s="46">
         <f>J18+J19</f>
         <v/>
       </c>
-      <c r="K21" s="45">
+      <c r="K21" s="46">
         <f>K18+K19</f>
         <v/>
       </c>
-      <c r="L21" s="45">
+      <c r="L21" s="46">
         <f>L18+L19</f>
         <v/>
       </c>
-      <c r="M21" s="45">
+      <c r="M21" s="46">
         <f>M18+M19</f>
         <v/>
       </c>
-      <c r="N21" s="45">
+      <c r="N21" s="46">
         <f>N18+N19</f>
         <v/>
       </c>
-      <c r="O21" s="45">
+      <c r="O21" s="46">
         <f>O18+O19</f>
         <v/>
       </c>
-      <c r="P21" s="45">
+      <c r="P21" s="46">
         <f>P18+P19</f>
         <v/>
       </c>
-      <c r="Q21" s="45">
+      <c r="Q21" s="46">
         <f>Q18+Q19</f>
         <v/>
       </c>
-      <c r="R21" s="45">
+      <c r="R21" s="46">
         <f>R18+R19</f>
         <v/>
       </c>
-      <c r="S21" s="45">
+      <c r="S21" s="46">
         <f>S18+S19</f>
         <v/>
       </c>
-      <c r="T21" s="45">
+      <c r="T21" s="46">
         <f>T18+T19</f>
         <v/>
       </c>
-      <c r="U21" s="45">
+      <c r="U21" s="46">
         <f>U18+U19</f>
         <v/>
       </c>
-      <c r="V21" s="45">
+      <c r="V21" s="46">
         <f>V18+V19</f>
         <v/>
       </c>
@@ -6486,7 +8046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -6588,7 +8148,7 @@
         <f>'Revenue Model'!E14</f>
         <v/>
       </c>
-      <c r="H5" s="46">
+      <c r="H5" s="39">
         <f>IF(F5=0,0,(G5-F5)/F5)</f>
         <v/>
       </c>
@@ -6700,11 +8260,11 @@
         <f>AVERAGE(C9:E9)</f>
         <v/>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="44">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="H9" s="46">
+      <c r="H9" s="39">
         <f>IF(F9=0,0,(G9-F9)/F9)</f>
         <v/>
       </c>
@@ -6742,7 +8302,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$88</f>
         <v/>
       </c>
-      <c r="H12" s="46">
+      <c r="H12" s="39">
         <f>IF(F12=0,0,(G12-F12)/F12)</f>
         <v/>
       </c>
@@ -6773,7 +8333,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$86</f>
         <v/>
       </c>
-      <c r="H13" s="46">
+      <c r="H13" s="39">
         <f>IF(F13=0,0,(G13-F13)/F13)</f>
         <v/>
       </c>
@@ -6804,7 +8364,7 @@
         <f>'Revenue Model'!E12*Inputs!$B$87</f>
         <v/>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="39">
         <f>IF(F14=0,0,(G14-F14)/F14)</f>
         <v/>
       </c>
@@ -7743,6 +9303,360 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E5496"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MVI 'Perfect Visit' Upside - illustrative growth above the conservative base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>ASSUMPTION (blue = adjust)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>MVI-driven census / referral uplift %</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>SCENARIO RESULTS (Year-2 annualized, SBA-only debt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Base (plan)</t>
+        </is>
+      </c>
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>+10%</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>+30%</t>
+        </is>
+      </c>
+      <c r="F8" s="30" t="inlineStr">
+        <is>
+          <t>MVI case</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Census / referral uplift</t>
+        </is>
+      </c>
+      <c r="B9" s="39">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="C9" s="39">
+        <f>0.10</f>
+        <v/>
+      </c>
+      <c r="D9" s="39">
+        <f>0.20</f>
+        <v/>
+      </c>
+      <c r="E9" s="39">
+        <f>0.30</f>
+        <v/>
+      </c>
+      <c r="F9" s="39">
+        <f>$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>Net revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="24">
+        <f>SUM('Operating Budget'!O6:R6)*(1+F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>Variable costs</t>
+        </is>
+      </c>
+      <c r="B11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+B9)</f>
+        <v/>
+      </c>
+      <c r="C11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+C9)</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+D9)</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+E9)</f>
+        <v/>
+      </c>
+      <c r="F11" s="24">
+        <f>-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))*(1+F9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>Fixed costs (held at plan)</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+      <c r="F12" s="24">
+        <f>-(SUM('Operating Budget'!O6:R6)-(SUM('Operating Budget'!O13:R13)+SUM('Operating Budget'!O22:R22)+SUM('Staffing &amp; Payroll'!O38:R38))-SUM('Operating Budget'!O24:R24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B13" s="27">
+        <f>B10+B11+B12</f>
+        <v/>
+      </c>
+      <c r="C13" s="27">
+        <f>C10+C11+C12</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>D10+D11+D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="27">
+        <f>E10+E11+E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="27">
+        <f>F10+F11+F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="inlineStr">
+        <is>
+          <t>EBITDA lift vs base</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>B13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>C13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>E13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>F13-SUM('Operating Budget'!O24:R24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>Net income (after D&amp;A, interest, tax)</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(B13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*B9</f>
+        <v/>
+      </c>
+      <c r="C15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(C13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*C9</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(D13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*D9</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(E13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*E9</f>
+        <v/>
+      </c>
+      <c r="F15" s="24">
+        <f>SUM('Operating Budget'!O34:R34)+(F13-SUM('Operating Budget'!O24:R24))-SUM('Operating Budget'!O33:R33)*F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>SBA debt service</t>
+        </is>
+      </c>
+      <c r="B16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="C16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+      <c r="F16" s="24">
+        <f>SUM('Debt Schedule'!O27:R27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="inlineStr">
+        <is>
+          <t>DSCR (SBA-only)</t>
+        </is>
+      </c>
+      <c r="B17" s="34">
+        <f>IF(B16=0,0,B13/B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="34">
+        <f>IF(C16=0,0,C13/C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="34">
+        <f>IF(D16=0,0,D13/D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="34">
+        <f>IF(E16=0,0,E13/E16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(F16=0,0,F13/F16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>Illustrative upside ONLY - not used for loan underwriting. The base case (Lender Summary / Business Plan Section 11) assumes no lift from the MVI 'Perfect Visit' / 'Perfect Phones' certification or Andrew Reid's national advertising campaign; SBA debt service is fully covered without it. This tab scales Year-2 census/referrals by the uplift while holding the cost base at plan (static roster); sustained higher census would trigger the model's capacity hiring, so realized EBITDA would run modestly below the static figures shown. Higher EBITDA also raises the equity exit value and MOIC on the Returns tab. For a full dynamic re-run, set Census scenario = Upside on the Inputs tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A19:F22"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -7803,7 +9717,7 @@
           <t>Blended GROSS rate ($/PD)</t>
         </is>
       </c>
-      <c r="B5" s="39">
+      <c r="B5" s="40">
         <f>Inputs!$B$20</f>
         <v/>
       </c>
@@ -7814,35 +9728,35 @@
           <t>Blended NET rate ($/PD)</t>
         </is>
       </c>
-      <c r="B6" s="39">
+      <c r="B6" s="40">
         <f>Inputs!$B$21</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="40" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O8" s="41" t="inlineStr">
+      <c r="O8" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S8" s="41" t="inlineStr">
+      <c r="S8" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="42" t="inlineStr"/>
+      <c r="A9" s="43" t="inlineStr"/>
       <c r="C9" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -7950,83 +9864,83 @@
           <t>Average daily census (ADC)</t>
         </is>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="44">
         <f>Inputs!C$33</f>
         <v/>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>Inputs!D$33</f>
         <v/>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="44">
         <f>Inputs!E$33</f>
         <v/>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="44">
         <f>Inputs!F$33</f>
         <v/>
       </c>
-      <c r="G10" s="43">
+      <c r="G10" s="44">
         <f>Inputs!G$33</f>
         <v/>
       </c>
-      <c r="H10" s="43">
+      <c r="H10" s="44">
         <f>Inputs!H$33</f>
         <v/>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="44">
         <f>Inputs!I$33</f>
         <v/>
       </c>
-      <c r="J10" s="43">
+      <c r="J10" s="44">
         <f>Inputs!J$33</f>
         <v/>
       </c>
-      <c r="K10" s="43">
+      <c r="K10" s="44">
         <f>Inputs!K$33</f>
         <v/>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="44">
         <f>Inputs!L$33</f>
         <v/>
       </c>
-      <c r="M10" s="43">
+      <c r="M10" s="44">
         <f>Inputs!M$33</f>
         <v/>
       </c>
-      <c r="N10" s="43">
+      <c r="N10" s="44">
         <f>Inputs!N$33</f>
         <v/>
       </c>
-      <c r="O10" s="43">
+      <c r="O10" s="44">
         <f>Inputs!O$33</f>
         <v/>
       </c>
-      <c r="P10" s="43">
+      <c r="P10" s="44">
         <f>Inputs!P$33</f>
         <v/>
       </c>
-      <c r="Q10" s="43">
+      <c r="Q10" s="44">
         <f>Inputs!Q$33</f>
         <v/>
       </c>
-      <c r="R10" s="43">
+      <c r="R10" s="44">
         <f>Inputs!R$33</f>
         <v/>
       </c>
-      <c r="S10" s="43">
+      <c r="S10" s="44">
         <f>Inputs!S$33</f>
         <v/>
       </c>
-      <c r="T10" s="43">
+      <c r="T10" s="44">
         <f>Inputs!T$33</f>
         <v/>
       </c>
-      <c r="U10" s="43">
+      <c r="U10" s="44">
         <f>Inputs!U$33</f>
         <v/>
       </c>
-      <c r="V10" s="43">
+      <c r="V10" s="44">
         <f>Inputs!V$33</f>
         <v/>
       </c>
@@ -8037,83 +9951,83 @@
           <t>Days in period</t>
         </is>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="G11" s="43">
+      <c r="G11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="H11" s="43">
+      <c r="H11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="J11" s="43">
+      <c r="J11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="K11" s="43">
+      <c r="K11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="M11" s="43">
+      <c r="M11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="N11" s="43">
+      <c r="N11" s="44">
         <f>Inputs!$B$25*1</f>
         <v/>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="P11" s="43">
+      <c r="P11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="Q11" s="43">
+      <c r="Q11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="R11" s="43">
+      <c r="R11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="S11" s="43">
+      <c r="S11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="T11" s="43">
+      <c r="T11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="U11" s="43">
+      <c r="U11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
-      <c r="V11" s="43">
+      <c r="V11" s="44">
         <f>Inputs!$B$25*3</f>
         <v/>
       </c>
@@ -8124,83 +10038,83 @@
           <t>Patient-days</t>
         </is>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="45">
         <f>C10*C11</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="45">
         <f>D10*D11</f>
         <v/>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="45">
         <f>E10*E11</f>
         <v/>
       </c>
-      <c r="F12" s="44">
+      <c r="F12" s="45">
         <f>F10*F11</f>
         <v/>
       </c>
-      <c r="G12" s="44">
+      <c r="G12" s="45">
         <f>G10*G11</f>
         <v/>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="45">
         <f>H10*H11</f>
         <v/>
       </c>
-      <c r="I12" s="44">
+      <c r="I12" s="45">
         <f>I10*I11</f>
         <v/>
       </c>
-      <c r="J12" s="44">
+      <c r="J12" s="45">
         <f>J10*J11</f>
         <v/>
       </c>
-      <c r="K12" s="44">
+      <c r="K12" s="45">
         <f>K10*K11</f>
         <v/>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="45">
         <f>L10*L11</f>
         <v/>
       </c>
-      <c r="M12" s="44">
+      <c r="M12" s="45">
         <f>M10*M11</f>
         <v/>
       </c>
-      <c r="N12" s="44">
+      <c r="N12" s="45">
         <f>N10*N11</f>
         <v/>
       </c>
-      <c r="O12" s="44">
+      <c r="O12" s="45">
         <f>O10*O11</f>
         <v/>
       </c>
-      <c r="P12" s="44">
+      <c r="P12" s="45">
         <f>P10*P11</f>
         <v/>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="45">
         <f>Q10*Q11</f>
         <v/>
       </c>
-      <c r="R12" s="44">
+      <c r="R12" s="45">
         <f>R10*R11</f>
         <v/>
       </c>
-      <c r="S12" s="44">
+      <c r="S12" s="45">
         <f>S10*S11</f>
         <v/>
       </c>
-      <c r="T12" s="44">
+      <c r="T12" s="45">
         <f>T10*T11</f>
         <v/>
       </c>
-      <c r="U12" s="44">
+      <c r="U12" s="45">
         <f>U10*U11</f>
         <v/>
       </c>
-      <c r="V12" s="44">
+      <c r="V12" s="45">
         <f>V10*V11</f>
         <v/>
       </c>
@@ -8559,83 +10473,83 @@
           <t>NET REVENUE</t>
         </is>
       </c>
-      <c r="C17" s="45">
+      <c r="C17" s="46">
         <f>C14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="D17" s="45">
+      <c r="D17" s="46">
         <f>D14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="E17" s="45">
+      <c r="E17" s="46">
         <f>E14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="F17" s="45">
+      <c r="F17" s="46">
         <f>F14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="G17" s="45">
+      <c r="G17" s="46">
         <f>G14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="H17" s="45">
+      <c r="H17" s="46">
         <f>H14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="46">
         <f>I14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="J17" s="45">
+      <c r="J17" s="46">
         <f>J14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="K17" s="45">
+      <c r="K17" s="46">
         <f>K14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="L17" s="45">
+      <c r="L17" s="46">
         <f>L14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="M17" s="45">
+      <c r="M17" s="46">
         <f>M14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="N17" s="45">
+      <c r="N17" s="46">
         <f>N14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="O17" s="45">
+      <c r="O17" s="46">
         <f>O14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="P17" s="45">
+      <c r="P17" s="46">
         <f>P14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="Q17" s="45">
+      <c r="Q17" s="46">
         <f>Q14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="R17" s="45">
+      <c r="R17" s="46">
         <f>R14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="S17" s="45">
+      <c r="S17" s="46">
         <f>S14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="T17" s="45">
+      <c r="T17" s="46">
         <f>T14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="U17" s="45">
+      <c r="U17" s="46">
         <f>U14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
-      <c r="V17" s="45">
+      <c r="V17" s="46">
         <f>V14*(1-Inputs!$B$10-Inputs!$B$11)</f>
         <v/>
       </c>
@@ -8740,7 +10654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -8789,29 +10703,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="41" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="41" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr"/>
+      <c r="A5" s="43" t="inlineStr"/>
       <c r="C5" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -8919,83 +10833,83 @@
           <t>ADC (driver)</t>
         </is>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="44">
         <f>'Revenue Model'!C10</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="44">
         <f>'Revenue Model'!D10</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="44">
         <f>'Revenue Model'!E10</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="44">
         <f>'Revenue Model'!F10</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="44">
         <f>'Revenue Model'!G10</f>
         <v/>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="44">
         <f>'Revenue Model'!H10</f>
         <v/>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="44">
         <f>'Revenue Model'!I10</f>
         <v/>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="44">
         <f>'Revenue Model'!J10</f>
         <v/>
       </c>
-      <c r="K6" s="43">
+      <c r="K6" s="44">
         <f>'Revenue Model'!K10</f>
         <v/>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="44">
         <f>'Revenue Model'!L10</f>
         <v/>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="44">
         <f>'Revenue Model'!M10</f>
         <v/>
       </c>
-      <c r="N6" s="43">
+      <c r="N6" s="44">
         <f>'Revenue Model'!N10</f>
         <v/>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="44">
         <f>'Revenue Model'!O10</f>
         <v/>
       </c>
-      <c r="P6" s="43">
+      <c r="P6" s="44">
         <f>'Revenue Model'!P10</f>
         <v/>
       </c>
-      <c r="Q6" s="43">
+      <c r="Q6" s="44">
         <f>'Revenue Model'!Q10</f>
         <v/>
       </c>
-      <c r="R6" s="43">
+      <c r="R6" s="44">
         <f>'Revenue Model'!R10</f>
         <v/>
       </c>
-      <c r="S6" s="43">
+      <c r="S6" s="44">
         <f>'Revenue Model'!S10</f>
         <v/>
       </c>
-      <c r="T6" s="43">
+      <c r="T6" s="44">
         <f>'Revenue Model'!T10</f>
         <v/>
       </c>
-      <c r="U6" s="43">
+      <c r="U6" s="44">
         <f>'Revenue Model'!U10</f>
         <v/>
       </c>
-      <c r="V6" s="43">
+      <c r="V6" s="44">
         <f>'Revenue Model'!V10</f>
         <v/>
       </c>
@@ -12340,83 +14254,83 @@
           <t>TOTAL DIRECT-CARE LABOR (COGS)</t>
         </is>
       </c>
-      <c r="C53" s="45">
+      <c r="C53" s="46">
         <f>C30+C38+C39+C48+C50</f>
         <v/>
       </c>
-      <c r="D53" s="45">
+      <c r="D53" s="46">
         <f>D30+D38+D39+D48+D50</f>
         <v/>
       </c>
-      <c r="E53" s="45">
+      <c r="E53" s="46">
         <f>E30+E38+E39+E48+E50</f>
         <v/>
       </c>
-      <c r="F53" s="45">
+      <c r="F53" s="46">
         <f>F30+F38+F39+F48+F50</f>
         <v/>
       </c>
-      <c r="G53" s="45">
+      <c r="G53" s="46">
         <f>G30+G38+G39+G48+G50</f>
         <v/>
       </c>
-      <c r="H53" s="45">
+      <c r="H53" s="46">
         <f>H30+H38+H39+H48+H50</f>
         <v/>
       </c>
-      <c r="I53" s="45">
+      <c r="I53" s="46">
         <f>I30+I38+I39+I48+I50</f>
         <v/>
       </c>
-      <c r="J53" s="45">
+      <c r="J53" s="46">
         <f>J30+J38+J39+J48+J50</f>
         <v/>
       </c>
-      <c r="K53" s="45">
+      <c r="K53" s="46">
         <f>K30+K38+K39+K48+K50</f>
         <v/>
       </c>
-      <c r="L53" s="45">
+      <c r="L53" s="46">
         <f>L30+L38+L39+L48+L50</f>
         <v/>
       </c>
-      <c r="M53" s="45">
+      <c r="M53" s="46">
         <f>M30+M38+M39+M48+M50</f>
         <v/>
       </c>
-      <c r="N53" s="45">
+      <c r="N53" s="46">
         <f>N30+N38+N39+N48+N50</f>
         <v/>
       </c>
-      <c r="O53" s="45">
+      <c r="O53" s="46">
         <f>O30+O38+O39+O48+O50</f>
         <v/>
       </c>
-      <c r="P53" s="45">
+      <c r="P53" s="46">
         <f>P30+P38+P39+P48+P50</f>
         <v/>
       </c>
-      <c r="Q53" s="45">
+      <c r="Q53" s="46">
         <f>Q30+Q38+Q39+Q48+Q50</f>
         <v/>
       </c>
-      <c r="R53" s="45">
+      <c r="R53" s="46">
         <f>R30+R38+R39+R48+R50</f>
         <v/>
       </c>
-      <c r="S53" s="45">
+      <c r="S53" s="46">
         <f>S30+S38+S39+S48+S50</f>
         <v/>
       </c>
-      <c r="T53" s="45">
+      <c r="T53" s="46">
         <f>T30+T38+T39+T48+T50</f>
         <v/>
       </c>
-      <c r="U53" s="45">
+      <c r="U53" s="46">
         <f>U30+U38+U39+U48+U50</f>
         <v/>
       </c>
-      <c r="V53" s="45">
+      <c r="V53" s="46">
         <f>V30+V38+V39+V48+V50</f>
         <v/>
       </c>
@@ -12427,83 +14341,83 @@
           <t>TOTAL INDIRECT LABOR (SG&amp;A)</t>
         </is>
       </c>
-      <c r="C54" s="45">
+      <c r="C54" s="46">
         <f>C42+C43+C49+C51</f>
         <v/>
       </c>
-      <c r="D54" s="45">
+      <c r="D54" s="46">
         <f>D42+D43+D49+D51</f>
         <v/>
       </c>
-      <c r="E54" s="45">
+      <c r="E54" s="46">
         <f>E42+E43+E49+E51</f>
         <v/>
       </c>
-      <c r="F54" s="45">
+      <c r="F54" s="46">
         <f>F42+F43+F49+F51</f>
         <v/>
       </c>
-      <c r="G54" s="45">
+      <c r="G54" s="46">
         <f>G42+G43+G49+G51</f>
         <v/>
       </c>
-      <c r="H54" s="45">
+      <c r="H54" s="46">
         <f>H42+H43+H49+H51</f>
         <v/>
       </c>
-      <c r="I54" s="45">
+      <c r="I54" s="46">
         <f>I42+I43+I49+I51</f>
         <v/>
       </c>
-      <c r="J54" s="45">
+      <c r="J54" s="46">
         <f>J42+J43+J49+J51</f>
         <v/>
       </c>
-      <c r="K54" s="45">
+      <c r="K54" s="46">
         <f>K42+K43+K49+K51</f>
         <v/>
       </c>
-      <c r="L54" s="45">
+      <c r="L54" s="46">
         <f>L42+L43+L49+L51</f>
         <v/>
       </c>
-      <c r="M54" s="45">
+      <c r="M54" s="46">
         <f>M42+M43+M49+M51</f>
         <v/>
       </c>
-      <c r="N54" s="45">
+      <c r="N54" s="46">
         <f>N42+N43+N49+N51</f>
         <v/>
       </c>
-      <c r="O54" s="45">
+      <c r="O54" s="46">
         <f>O42+O43+O49+O51</f>
         <v/>
       </c>
-      <c r="P54" s="45">
+      <c r="P54" s="46">
         <f>P42+P43+P49+P51</f>
         <v/>
       </c>
-      <c r="Q54" s="45">
+      <c r="Q54" s="46">
         <f>Q42+Q43+Q49+Q51</f>
         <v/>
       </c>
-      <c r="R54" s="45">
+      <c r="R54" s="46">
         <f>R42+R43+R49+R51</f>
         <v/>
       </c>
-      <c r="S54" s="45">
+      <c r="S54" s="46">
         <f>S42+S43+S49+S51</f>
         <v/>
       </c>
-      <c r="T54" s="45">
+      <c r="T54" s="46">
         <f>T42+T43+T49+T51</f>
         <v/>
       </c>
-      <c r="U54" s="45">
+      <c r="U54" s="46">
         <f>U42+U43+U49+U51</f>
         <v/>
       </c>
-      <c r="V54" s="45">
+      <c r="V54" s="46">
         <f>V42+V43+V49+V51</f>
         <v/>
       </c>
@@ -12524,7 +14438,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -12573,29 +14487,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="40" t="inlineStr">
+      <c r="A4" s="41" t="inlineStr">
         <is>
           <t>($ per period)</t>
         </is>
       </c>
-      <c r="C4" s="41" t="inlineStr">
+      <c r="C4" s="42" t="inlineStr">
         <is>
           <t>YEAR 1 - monthly</t>
         </is>
       </c>
-      <c r="O4" s="41" t="inlineStr">
+      <c r="O4" s="42" t="inlineStr">
         <is>
           <t>YEAR 2 - quarterly</t>
         </is>
       </c>
-      <c r="S4" s="41" t="inlineStr">
+      <c r="S4" s="42" t="inlineStr">
         <is>
           <t>YEAR 3 - quarterly</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="42" t="inlineStr"/>
+      <c r="A5" s="43" t="inlineStr"/>
       <c r="C5" s="30" t="inlineStr">
         <is>
           <t>M1</t>
@@ -13319,83 +15233,83 @@
           <t>GROSS PROFIT</t>
         </is>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="46">
         <f>C6-C14</f>
         <v/>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="46">
         <f>D6-D14</f>
         <v/>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="46">
         <f>E6-E14</f>
         <v/>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="46">
         <f>F6-F14</f>
         <v/>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="46">
         <f>G6-G14</f>
         <v/>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="46">
         <f>H6-H14</f>
         <v/>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="46">
         <f>I6-I14</f>
         <v/>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="46">
         <f>J6-J14</f>
         <v/>
       </c>
-      <c r="K15" s="45">
+      <c r="K15" s="46">
         <f>K6-K14</f>
         <v/>
       </c>
-      <c r="L15" s="45">
+      <c r="L15" s="46">
         <f>L6-L14</f>
         <v/>
       </c>
-      <c r="M15" s="45">
+      <c r="M15" s="46">
         <f>M6-M14</f>
         <v/>
       </c>
-      <c r="N15" s="45">
+      <c r="N15" s="46">
         <f>N6-N14</f>
         <v/>
       </c>
-      <c r="O15" s="45">
+      <c r="O15" s="46">
         <f>O6-O14</f>
         <v/>
       </c>
-      <c r="P15" s="45">
+      <c r="P15" s="46">
         <f>P6-P14</f>
         <v/>
       </c>
-      <c r="Q15" s="45">
+      <c r="Q15" s="46">
         <f>Q6-Q14</f>
         <v/>
       </c>
-      <c r="R15" s="45">
+      <c r="R15" s="46">
         <f>R6-R14</f>
         <v/>
       </c>
-      <c r="S15" s="45">
+      <c r="S15" s="46">
         <f>S6-S14</f>
         <v/>
       </c>
-      <c r="T15" s="45">
+      <c r="T15" s="46">
         <f>T6-T14</f>
         <v/>
       </c>
-      <c r="U15" s="45">
+      <c r="U15" s="46">
         <f>U6-U14</f>
         <v/>
       </c>
-      <c r="V15" s="45">
+      <c r="V15" s="46">
         <f>V6-V14</f>
         <v/>
       </c>
@@ -13406,83 +15320,83 @@
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C16" s="46">
+      <c r="C16" s="39">
         <f>IF(C6=0,0,C15/C6)</f>
         <v/>
       </c>
-      <c r="D16" s="46">
+      <c r="D16" s="39">
         <f>IF(D6=0,0,D15/D6)</f>
         <v/>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="39">
         <f>IF(E6=0,0,E15/E6)</f>
         <v/>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="39">
         <f>IF(F6=0,0,F15/F6)</f>
         <v/>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="39">
         <f>IF(G6=0,0,G15/G6)</f>
         <v/>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="39">
         <f>IF(H6=0,0,H15/H6)</f>
         <v/>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="39">
         <f>IF(I6=0,0,I15/I6)</f>
         <v/>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="39">
         <f>IF(J6=0,0,J15/J6)</f>
         <v/>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="39">
         <f>IF(K6=0,0,K15/K6)</f>
         <v/>
       </c>
-      <c r="L16" s="46">
+      <c r="L16" s="39">
         <f>IF(L6=0,0,L15/L6)</f>
         <v/>
       </c>
-      <c r="M16" s="46">
+      <c r="M16" s="39">
         <f>IF(M6=0,0,M15/M6)</f>
         <v/>
       </c>
-      <c r="N16" s="46">
+      <c r="N16" s="39">
         <f>IF(N6=0,0,N15/N6)</f>
         <v/>
       </c>
-      <c r="O16" s="46">
+      <c r="O16" s="39">
         <f>IF(O6=0,0,O15/O6)</f>
         <v/>
       </c>
-      <c r="P16" s="46">
+      <c r="P16" s="39">
         <f>IF(P6=0,0,P15/P6)</f>
         <v/>
       </c>
-      <c r="Q16" s="46">
+      <c r="Q16" s="39">
         <f>IF(Q6=0,0,Q15/Q6)</f>
         <v/>
       </c>
-      <c r="R16" s="46">
+      <c r="R16" s="39">
         <f>IF(R6=0,0,R15/R6)</f>
         <v/>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="39">
         <f>IF(S6=0,0,S15/S6)</f>
         <v/>
       </c>
-      <c r="T16" s="46">
+      <c r="T16" s="39">
         <f>IF(T6=0,0,T15/T6)</f>
         <v/>
       </c>
-      <c r="U16" s="46">
+      <c r="U16" s="39">
         <f>IF(U6=0,0,U15/U6)</f>
         <v/>
       </c>
-      <c r="V16" s="46">
+      <c r="V16" s="39">
         <f>IF(V6=0,0,V15/V6)</f>
         <v/>
       </c>
@@ -14022,83 +15936,83 @@
           <t>EBITDA margin %</t>
         </is>
       </c>
-      <c r="C25" s="46">
+      <c r="C25" s="39">
         <f>IF(C6=0,0,C24/C6)</f>
         <v/>
       </c>
-      <c r="D25" s="46">
+      <c r="D25" s="39">
         <f>IF(D6=0,0,D24/D6)</f>
         <v/>
       </c>
-      <c r="E25" s="46">
+      <c r="E25" s="39">
         <f>IF(E6=0,0,E24/E6)</f>
         <v/>
       </c>
-      <c r="F25" s="46">
+      <c r="F25" s="39">
         <f>IF(F6=0,0,F24/F6)</f>
         <v/>
       </c>
-      <c r="G25" s="46">
+      <c r="G25" s="39">
         <f>IF(G6=0,0,G24/G6)</f>
         <v/>
       </c>
-      <c r="H25" s="46">
+      <c r="H25" s="39">
         <f>IF(H6=0,0,H24/H6)</f>
         <v/>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="39">
         <f>IF(I6=0,0,I24/I6)</f>
         <v/>
       </c>
-      <c r="J25" s="46">
+      <c r="J25" s="39">
         <f>IF(J6=0,0,J24/J6)</f>
         <v/>
       </c>
-      <c r="K25" s="46">
+      <c r="K25" s="39">
         <f>IF(K6=0,0,K24/K6)</f>
         <v/>
       </c>
-      <c r="L25" s="46">
+      <c r="L25" s="39">
         <f>IF(L6=0,0,L24/L6)</f>
         <v/>
       </c>
-      <c r="M25" s="46">
+      <c r="M25" s="39">
         <f>IF(M6=0,0,M24/M6)</f>
         <v/>
       </c>
-      <c r="N25" s="46">
+      <c r="N25" s="39">
         <f>IF(N6=0,0,N24/N6)</f>
         <v/>
       </c>
-      <c r="O25" s="46">
+      <c r="O25" s="39">
         <f>IF(O6=0,0,O24/O6)</f>
         <v/>
       </c>
-      <c r="P25" s="46">
+      <c r="P25" s="39">
         <f>IF(P6=0,0,P24/P6)</f>
         <v/>
       </c>
-      <c r="Q25" s="46">
+      <c r="Q25" s="39">
         <f>IF(Q6=0,0,Q24/Q6)</f>
         <v/>
       </c>
-      <c r="R25" s="46">
+      <c r="R25" s="39">
         <f>IF(R6=0,0,R24/R6)</f>
         <v/>
       </c>
-      <c r="S25" s="46">
+      <c r="S25" s="39">
         <f>IF(S6=0,0,S24/S6)</f>
         <v/>
       </c>
-      <c r="T25" s="46">
+      <c r="T25" s="39">
         <f>IF(T6=0,0,T24/T6)</f>
         <v/>
       </c>
-      <c r="U25" s="46">
+      <c r="U25" s="39">
         <f>IF(U6=0,0,U24/U6)</f>
         <v/>
       </c>
-      <c r="V25" s="46">
+      <c r="V25" s="39">
         <f>IF(V6=0,0,V24/V6)</f>
         <v/>
       </c>
@@ -14638,83 +16552,83 @@
           <t>NET INCOME</t>
         </is>
       </c>
-      <c r="C34" s="45">
+      <c r="C34" s="46">
         <f>C32-C33</f>
         <v/>
       </c>
-      <c r="D34" s="45">
+      <c r="D34" s="46">
         <f>D32-D33</f>
         <v/>
       </c>
-      <c r="E34" s="45">
+      <c r="E34" s="46">
         <f>E32-E33</f>
         <v/>
       </c>
-      <c r="F34" s="45">
+      <c r="F34" s="46">
         <f>F32-F33</f>
         <v/>
       </c>
-      <c r="G34" s="45">
+      <c r="G34" s="46">
         <f>G32-G33</f>
         <v/>
       </c>
-      <c r="H34" s="45">
+      <c r="H34" s="46">
         <f>H32-H33</f>
         <v/>
       </c>
-      <c r="I34" s="45">
+      <c r="I34" s="46">
         <f>I32-I33</f>
         <v/>
       </c>
-      <c r="J34" s="45">
+      <c r="J34" s="46">
         <f>J32-J33</f>
         <v/>
       </c>
-      <c r="K34" s="45">
+      <c r="K34" s="46">
         <f>K32-K33</f>
         <v/>
       </c>
-      <c r="L34" s="45">
+      <c r="L34" s="46">
         <f>L32-L33</f>
         <v/>
       </c>
-      <c r="M34" s="45">
+      <c r="M34" s="46">
         <f>M32-M33</f>
         <v/>
       </c>
-      <c r="N34" s="45">
+      <c r="N34" s="46">
         <f>N32-N33</f>
         <v/>
       </c>
-      <c r="O34" s="45">
+      <c r="O34" s="46">
         <f>O32-O33</f>
         <v/>
       </c>
-      <c r="P34" s="45">
+      <c r="P34" s="46">
         <f>P32-P33</f>
         <v/>
       </c>
-      <c r="Q34" s="45">
+      <c r="Q34" s="46">
         <f>Q32-Q33</f>
         <v/>
       </c>
-      <c r="R34" s="45">
+      <c r="R34" s="46">
         <f>R32-R33</f>
         <v/>
       </c>
-      <c r="S34" s="45">
+      <c r="S34" s="46">
         <f>S32-S33</f>
         <v/>
       </c>
-      <c r="T34" s="45">
+      <c r="T34" s="46">
         <f>T32-T33</f>
         <v/>
       </c>
-      <c r="U34" s="45">
+      <c r="U34" s="46">
         <f>U32-U33</f>
         <v/>
       </c>
-      <c r="V34" s="45">
+      <c r="V34" s="46">
         <f>V32-V33</f>
         <v/>
       </c>
@@ -14734,7 +16648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00808080"/>
@@ -18393,1548 +20307,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00808080"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:V29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
-    <col width="11" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>AZALEA HOSPICE &amp; PALLIATIVE CARE - Tyler, TX</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Debt Schedule - SBA 7(a) only (seller paid at close) | DSCR shown (target &gt;= 1.25x)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>LOAN TERMS (from Inputs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SBA monthly payment (PMT)</t>
-        </is>
-      </c>
-      <c r="B5" s="24">
-        <f>PMT(Inputs!$B$111/12,Inputs!$B$112,-Inputs!$B$110)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>License note monthly payment (PMT)</t>
-        </is>
-      </c>
-      <c r="B6" s="24">
-        <f>0</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="40" t="inlineStr">
-        <is>
-          <t>($ per period)</t>
-        </is>
-      </c>
-      <c r="C8" s="41" t="inlineStr">
-        <is>
-          <t>YEAR 1 - monthly</t>
-        </is>
-      </c>
-      <c r="O8" s="41" t="inlineStr">
-        <is>
-          <t>YEAR 2 - quarterly</t>
-        </is>
-      </c>
-      <c r="S8" s="41" t="inlineStr">
-        <is>
-          <t>YEAR 3 - quarterly</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="42" t="inlineStr"/>
-      <c r="C9" s="30" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="D9" s="30" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="E9" s="30" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="F9" s="30" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="G9" s="30" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="H9" s="30" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="I9" s="30" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="J9" s="30" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="K9" s="30" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="L9" s="30" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="M9" s="30" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="N9" s="30" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="O9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q1</t>
-        </is>
-      </c>
-      <c r="P9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q2</t>
-        </is>
-      </c>
-      <c r="Q9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q3</t>
-        </is>
-      </c>
-      <c r="R9" s="30" t="inlineStr">
-        <is>
-          <t>Y2 Q4</t>
-        </is>
-      </c>
-      <c r="S9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q1</t>
-        </is>
-      </c>
-      <c r="T9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q2</t>
-        </is>
-      </c>
-      <c r="U9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q3</t>
-        </is>
-      </c>
-      <c r="V9" s="30" t="inlineStr">
-        <is>
-          <t>Y3 Q4</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>SBA 7(a) LOAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="inlineStr">
-        <is>
-          <t>Beginning balance</t>
-        </is>
-      </c>
-      <c r="C11" s="25">
-        <f>Inputs!$B$110</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>C15</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>D15</f>
-        <v/>
-      </c>
-      <c r="F11" s="24">
-        <f>E15</f>
-        <v/>
-      </c>
-      <c r="G11" s="24">
-        <f>F15</f>
-        <v/>
-      </c>
-      <c r="H11" s="24">
-        <f>G15</f>
-        <v/>
-      </c>
-      <c r="I11" s="24">
-        <f>H15</f>
-        <v/>
-      </c>
-      <c r="J11" s="24">
-        <f>I15</f>
-        <v/>
-      </c>
-      <c r="K11" s="24">
-        <f>J15</f>
-        <v/>
-      </c>
-      <c r="L11" s="24">
-        <f>K15</f>
-        <v/>
-      </c>
-      <c r="M11" s="24">
-        <f>L15</f>
-        <v/>
-      </c>
-      <c r="N11" s="24">
-        <f>M15</f>
-        <v/>
-      </c>
-      <c r="O11" s="24">
-        <f>N15</f>
-        <v/>
-      </c>
-      <c r="P11" s="24">
-        <f>O15</f>
-        <v/>
-      </c>
-      <c r="Q11" s="24">
-        <f>P15</f>
-        <v/>
-      </c>
-      <c r="R11" s="24">
-        <f>Q15</f>
-        <v/>
-      </c>
-      <c r="S11" s="24">
-        <f>R15</f>
-        <v/>
-      </c>
-      <c r="T11" s="24">
-        <f>S15</f>
-        <v/>
-      </c>
-      <c r="U11" s="24">
-        <f>T15</f>
-        <v/>
-      </c>
-      <c r="V11" s="24">
-        <f>U15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Payment</t>
-        </is>
-      </c>
-      <c r="C12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="F12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="G12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="H12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="I12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="J12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="K12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="L12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="M12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="N12" s="24">
-        <f>'Debt Schedule'!$B$5*1</f>
-        <v/>
-      </c>
-      <c r="O12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="P12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="Q12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="R12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="S12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="T12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="U12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-      <c r="V12" s="24">
-        <f>'Debt Schedule'!$B$5*3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="C13" s="24">
-        <f>C11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>D11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>E11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="F13" s="24">
-        <f>F11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="G13" s="24">
-        <f>G11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="H13" s="24">
-        <f>H11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="I13" s="24">
-        <f>I11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="J13" s="24">
-        <f>J11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="K13" s="24">
-        <f>K11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="L13" s="24">
-        <f>L11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="M13" s="24">
-        <f>M11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="N13" s="24">
-        <f>N11*Inputs!$B$111/12*1</f>
-        <v/>
-      </c>
-      <c r="O13" s="24">
-        <f>O11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="P13" s="24">
-        <f>P11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="Q13" s="24">
-        <f>Q11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="R13" s="24">
-        <f>R11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="S13" s="24">
-        <f>S11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="T13" s="24">
-        <f>T11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="U13" s="24">
-        <f>U11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-      <c r="V13" s="24">
-        <f>V11*Inputs!$B$111/12*3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="C14" s="24">
-        <f>C12-C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>D12-D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="24">
-        <f>E12-E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="24">
-        <f>F12-F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="24">
-        <f>G12-G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="24">
-        <f>H12-H13</f>
-        <v/>
-      </c>
-      <c r="I14" s="24">
-        <f>I12-I13</f>
-        <v/>
-      </c>
-      <c r="J14" s="24">
-        <f>J12-J13</f>
-        <v/>
-      </c>
-      <c r="K14" s="24">
-        <f>K12-K13</f>
-        <v/>
-      </c>
-      <c r="L14" s="24">
-        <f>L12-L13</f>
-        <v/>
-      </c>
-      <c r="M14" s="24">
-        <f>M12-M13</f>
-        <v/>
-      </c>
-      <c r="N14" s="24">
-        <f>N12-N13</f>
-        <v/>
-      </c>
-      <c r="O14" s="24">
-        <f>O12-O13</f>
-        <v/>
-      </c>
-      <c r="P14" s="24">
-        <f>P12-P13</f>
-        <v/>
-      </c>
-      <c r="Q14" s="24">
-        <f>Q12-Q13</f>
-        <v/>
-      </c>
-      <c r="R14" s="24">
-        <f>R12-R13</f>
-        <v/>
-      </c>
-      <c r="S14" s="24">
-        <f>S12-S13</f>
-        <v/>
-      </c>
-      <c r="T14" s="24">
-        <f>T12-T13</f>
-        <v/>
-      </c>
-      <c r="U14" s="24">
-        <f>U12-U13</f>
-        <v/>
-      </c>
-      <c r="V14" s="24">
-        <f>V12-V13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>Ending balance</t>
-        </is>
-      </c>
-      <c r="C15" s="23">
-        <f>C11-C14</f>
-        <v/>
-      </c>
-      <c r="D15" s="23">
-        <f>D11-D14</f>
-        <v/>
-      </c>
-      <c r="E15" s="23">
-        <f>E11-E14</f>
-        <v/>
-      </c>
-      <c r="F15" s="23">
-        <f>F11-F14</f>
-        <v/>
-      </c>
-      <c r="G15" s="23">
-        <f>G11-G14</f>
-        <v/>
-      </c>
-      <c r="H15" s="23">
-        <f>H11-H14</f>
-        <v/>
-      </c>
-      <c r="I15" s="23">
-        <f>I11-I14</f>
-        <v/>
-      </c>
-      <c r="J15" s="23">
-        <f>J11-J14</f>
-        <v/>
-      </c>
-      <c r="K15" s="23">
-        <f>K11-K14</f>
-        <v/>
-      </c>
-      <c r="L15" s="23">
-        <f>L11-L14</f>
-        <v/>
-      </c>
-      <c r="M15" s="23">
-        <f>M11-M14</f>
-        <v/>
-      </c>
-      <c r="N15" s="23">
-        <f>N11-N14</f>
-        <v/>
-      </c>
-      <c r="O15" s="23">
-        <f>O11-O14</f>
-        <v/>
-      </c>
-      <c r="P15" s="23">
-        <f>P11-P14</f>
-        <v/>
-      </c>
-      <c r="Q15" s="23">
-        <f>Q11-Q14</f>
-        <v/>
-      </c>
-      <c r="R15" s="23">
-        <f>R11-R14</f>
-        <v/>
-      </c>
-      <c r="S15" s="23">
-        <f>S11-S14</f>
-        <v/>
-      </c>
-      <c r="T15" s="23">
-        <f>T11-T14</f>
-        <v/>
-      </c>
-      <c r="U15" s="23">
-        <f>U11-U14</f>
-        <v/>
-      </c>
-      <c r="V15" s="23">
-        <f>V11-V14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>HICKORY LICENSE - PAID AT CLOSE (no seller note; schedule zeroed)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="inlineStr">
-        <is>
-          <t>Beginning balance</t>
-        </is>
-      </c>
-      <c r="C18" s="25">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>C22</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>D22</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>E22</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
-        <f>F22</f>
-        <v/>
-      </c>
-      <c r="H18" s="24">
-        <f>G22</f>
-        <v/>
-      </c>
-      <c r="I18" s="24">
-        <f>H22</f>
-        <v/>
-      </c>
-      <c r="J18" s="24">
-        <f>I22</f>
-        <v/>
-      </c>
-      <c r="K18" s="24">
-        <f>J22</f>
-        <v/>
-      </c>
-      <c r="L18" s="24">
-        <f>K22</f>
-        <v/>
-      </c>
-      <c r="M18" s="24">
-        <f>L22</f>
-        <v/>
-      </c>
-      <c r="N18" s="24">
-        <f>M22</f>
-        <v/>
-      </c>
-      <c r="O18" s="24">
-        <f>N22</f>
-        <v/>
-      </c>
-      <c r="P18" s="24">
-        <f>O22</f>
-        <v/>
-      </c>
-      <c r="Q18" s="24">
-        <f>P22</f>
-        <v/>
-      </c>
-      <c r="R18" s="24">
-        <f>Q22</f>
-        <v/>
-      </c>
-      <c r="S18" s="24">
-        <f>R22</f>
-        <v/>
-      </c>
-      <c r="T18" s="24">
-        <f>S22</f>
-        <v/>
-      </c>
-      <c r="U18" s="24">
-        <f>T22</f>
-        <v/>
-      </c>
-      <c r="V18" s="24">
-        <f>U22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>Ending balance (closed-form)</t>
-        </is>
-      </c>
-      <c r="C19" s="24">
-        <f>MAX(0,C18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>MAX(0,D18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>MAX(0,E18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>MAX(0,F18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
-        <f>MAX(0,G18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="H19" s="24">
-        <f>MAX(0,H18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
-        <f>MAX(0,I18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>MAX(0,J18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="K19" s="24">
-        <f>MAX(0,K18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="L19" s="24">
-        <f>MAX(0,L18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="M19" s="24">
-        <f>MAX(0,M18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>MAX(0,N18*(1+Inputs!$B$121/12)^1-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^1-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="O19" s="24">
-        <f>MAX(0,O18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="P19" s="24">
-        <f>MAX(0,P18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="24">
-        <f>MAX(0,Q18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="R19" s="24">
-        <f>MAX(0,R18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="S19" s="24">
-        <f>MAX(0,S18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="T19" s="24">
-        <f>MAX(0,T18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="U19" s="24">
-        <f>MAX(0,U18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-      <c r="V19" s="24">
-        <f>MAX(0,V18*(1+Inputs!$B$121/12)^3-'Debt Schedule'!$B$6*((1+Inputs!$B$121/12)^3-1)/(Inputs!$B$121/12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="C20" s="24">
-        <f>C18-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>D18-D19</f>
-        <v/>
-      </c>
-      <c r="E20" s="24">
-        <f>E18-E19</f>
-        <v/>
-      </c>
-      <c r="F20" s="24">
-        <f>F18-F19</f>
-        <v/>
-      </c>
-      <c r="G20" s="24">
-        <f>G18-G19</f>
-        <v/>
-      </c>
-      <c r="H20" s="24">
-        <f>H18-H19</f>
-        <v/>
-      </c>
-      <c r="I20" s="24">
-        <f>I18-I19</f>
-        <v/>
-      </c>
-      <c r="J20" s="24">
-        <f>J18-J19</f>
-        <v/>
-      </c>
-      <c r="K20" s="24">
-        <f>K18-K19</f>
-        <v/>
-      </c>
-      <c r="L20" s="24">
-        <f>L18-L19</f>
-        <v/>
-      </c>
-      <c r="M20" s="24">
-        <f>M18-M19</f>
-        <v/>
-      </c>
-      <c r="N20" s="24">
-        <f>N18-N19</f>
-        <v/>
-      </c>
-      <c r="O20" s="24">
-        <f>O18-O19</f>
-        <v/>
-      </c>
-      <c r="P20" s="24">
-        <f>P18-P19</f>
-        <v/>
-      </c>
-      <c r="Q20" s="24">
-        <f>Q18-Q19</f>
-        <v/>
-      </c>
-      <c r="R20" s="24">
-        <f>R18-R19</f>
-        <v/>
-      </c>
-      <c r="S20" s="24">
-        <f>S18-S19</f>
-        <v/>
-      </c>
-      <c r="T20" s="24">
-        <f>T18-T19</f>
-        <v/>
-      </c>
-      <c r="U20" s="24">
-        <f>U18-U19</f>
-        <v/>
-      </c>
-      <c r="V20" s="24">
-        <f>V18-V19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Interest</t>
-        </is>
-      </c>
-      <c r="C21" s="24">
-        <f>MAX(0,IF(C18=0,0,'Debt Schedule'!$B$6*1-C20))</f>
-        <v/>
-      </c>
-      <c r="D21" s="24">
-        <f>MAX(0,IF(D18=0,0,'Debt Schedule'!$B$6*1-D20))</f>
-        <v/>
-      </c>
-      <c r="E21" s="24">
-        <f>MAX(0,IF(E18=0,0,'Debt Schedule'!$B$6*1-E20))</f>
-        <v/>
-      </c>
-      <c r="F21" s="24">
-        <f>MAX(0,IF(F18=0,0,'Debt Schedule'!$B$6*1-F20))</f>
-        <v/>
-      </c>
-      <c r="G21" s="24">
-        <f>MAX(0,IF(G18=0,0,'Debt Schedule'!$B$6*1-G20))</f>
-        <v/>
-      </c>
-      <c r="H21" s="24">
-        <f>MAX(0,IF(H18=0,0,'Debt Schedule'!$B$6*1-H20))</f>
-        <v/>
-      </c>
-      <c r="I21" s="24">
-        <f>MAX(0,IF(I18=0,0,'Debt Schedule'!$B$6*1-I20))</f>
-        <v/>
-      </c>
-      <c r="J21" s="24">
-        <f>MAX(0,IF(J18=0,0,'Debt Schedule'!$B$6*1-J20))</f>
-        <v/>
-      </c>
-      <c r="K21" s="24">
-        <f>MAX(0,IF(K18=0,0,'Debt Schedule'!$B$6*1-K20))</f>
-        <v/>
-      </c>
-      <c r="L21" s="24">
-        <f>MAX(0,IF(L18=0,0,'Debt Schedule'!$B$6*1-L20))</f>
-        <v/>
-      </c>
-      <c r="M21" s="24">
-        <f>MAX(0,IF(M18=0,0,'Debt Schedule'!$B$6*1-M20))</f>
-        <v/>
-      </c>
-      <c r="N21" s="24">
-        <f>MAX(0,IF(N18=0,0,'Debt Schedule'!$B$6*1-N20))</f>
-        <v/>
-      </c>
-      <c r="O21" s="24">
-        <f>MAX(0,IF(O18=0,0,'Debt Schedule'!$B$6*3-O20))</f>
-        <v/>
-      </c>
-      <c r="P21" s="24">
-        <f>MAX(0,IF(P18=0,0,'Debt Schedule'!$B$6*3-P20))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="24">
-        <f>MAX(0,IF(Q18=0,0,'Debt Schedule'!$B$6*3-Q20))</f>
-        <v/>
-      </c>
-      <c r="R21" s="24">
-        <f>MAX(0,IF(R18=0,0,'Debt Schedule'!$B$6*3-R20))</f>
-        <v/>
-      </c>
-      <c r="S21" s="24">
-        <f>MAX(0,IF(S18=0,0,'Debt Schedule'!$B$6*3-S20))</f>
-        <v/>
-      </c>
-      <c r="T21" s="24">
-        <f>MAX(0,IF(T18=0,0,'Debt Schedule'!$B$6*3-T20))</f>
-        <v/>
-      </c>
-      <c r="U21" s="24">
-        <f>MAX(0,IF(U18=0,0,'Debt Schedule'!$B$6*3-U20))</f>
-        <v/>
-      </c>
-      <c r="V21" s="24">
-        <f>MAX(0,IF(V18=0,0,'Debt Schedule'!$B$6*3-V20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="26" t="inlineStr">
-        <is>
-          <t>Ending balance</t>
-        </is>
-      </c>
-      <c r="C22" s="23">
-        <f>C19</f>
-        <v/>
-      </c>
-      <c r="D22" s="23">
-        <f>D19</f>
-        <v/>
-      </c>
-      <c r="E22" s="23">
-        <f>E19</f>
-        <v/>
-      </c>
-      <c r="F22" s="23">
-        <f>F19</f>
-        <v/>
-      </c>
-      <c r="G22" s="23">
-        <f>G19</f>
-        <v/>
-      </c>
-      <c r="H22" s="23">
-        <f>H19</f>
-        <v/>
-      </c>
-      <c r="I22" s="23">
-        <f>I19</f>
-        <v/>
-      </c>
-      <c r="J22" s="23">
-        <f>J19</f>
-        <v/>
-      </c>
-      <c r="K22" s="23">
-        <f>K19</f>
-        <v/>
-      </c>
-      <c r="L22" s="23">
-        <f>L19</f>
-        <v/>
-      </c>
-      <c r="M22" s="23">
-        <f>M19</f>
-        <v/>
-      </c>
-      <c r="N22" s="23">
-        <f>N19</f>
-        <v/>
-      </c>
-      <c r="O22" s="23">
-        <f>O19</f>
-        <v/>
-      </c>
-      <c r="P22" s="23">
-        <f>P19</f>
-        <v/>
-      </c>
-      <c r="Q22" s="23">
-        <f>Q19</f>
-        <v/>
-      </c>
-      <c r="R22" s="23">
-        <f>R19</f>
-        <v/>
-      </c>
-      <c r="S22" s="23">
-        <f>S19</f>
-        <v/>
-      </c>
-      <c r="T22" s="23">
-        <f>T19</f>
-        <v/>
-      </c>
-      <c r="U22" s="23">
-        <f>U19</f>
-        <v/>
-      </c>
-      <c r="V22" s="23">
-        <f>V19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>DEBT SERVICE &amp; COVERAGE (SBA only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
-        <is>
-          <t>Total interest</t>
-        </is>
-      </c>
-      <c r="C25" s="24">
-        <f>C13+C21</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>D13+D21</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>E13+E21</f>
-        <v/>
-      </c>
-      <c r="F25" s="24">
-        <f>F13+F21</f>
-        <v/>
-      </c>
-      <c r="G25" s="24">
-        <f>G13+G21</f>
-        <v/>
-      </c>
-      <c r="H25" s="24">
-        <f>H13+H21</f>
-        <v/>
-      </c>
-      <c r="I25" s="24">
-        <f>I13+I21</f>
-        <v/>
-      </c>
-      <c r="J25" s="24">
-        <f>J13+J21</f>
-        <v/>
-      </c>
-      <c r="K25" s="24">
-        <f>K13+K21</f>
-        <v/>
-      </c>
-      <c r="L25" s="24">
-        <f>L13+L21</f>
-        <v/>
-      </c>
-      <c r="M25" s="24">
-        <f>M13+M21</f>
-        <v/>
-      </c>
-      <c r="N25" s="24">
-        <f>N13+N21</f>
-        <v/>
-      </c>
-      <c r="O25" s="24">
-        <f>O13+O21</f>
-        <v/>
-      </c>
-      <c r="P25" s="24">
-        <f>P13+P21</f>
-        <v/>
-      </c>
-      <c r="Q25" s="24">
-        <f>Q13+Q21</f>
-        <v/>
-      </c>
-      <c r="R25" s="24">
-        <f>R13+R21</f>
-        <v/>
-      </c>
-      <c r="S25" s="24">
-        <f>S13+S21</f>
-        <v/>
-      </c>
-      <c r="T25" s="24">
-        <f>T13+T21</f>
-        <v/>
-      </c>
-      <c r="U25" s="24">
-        <f>U13+U21</f>
-        <v/>
-      </c>
-      <c r="V25" s="24">
-        <f>V13+V21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
-        <is>
-          <t>Total principal</t>
-        </is>
-      </c>
-      <c r="C26" s="24">
-        <f>C14+C20</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>D14+D20</f>
-        <v/>
-      </c>
-      <c r="E26" s="24">
-        <f>E14+E20</f>
-        <v/>
-      </c>
-      <c r="F26" s="24">
-        <f>F14+F20</f>
-        <v/>
-      </c>
-      <c r="G26" s="24">
-        <f>G14+G20</f>
-        <v/>
-      </c>
-      <c r="H26" s="24">
-        <f>H14+H20</f>
-        <v/>
-      </c>
-      <c r="I26" s="24">
-        <f>I14+I20</f>
-        <v/>
-      </c>
-      <c r="J26" s="24">
-        <f>J14+J20</f>
-        <v/>
-      </c>
-      <c r="K26" s="24">
-        <f>K14+K20</f>
-        <v/>
-      </c>
-      <c r="L26" s="24">
-        <f>L14+L20</f>
-        <v/>
-      </c>
-      <c r="M26" s="24">
-        <f>M14+M20</f>
-        <v/>
-      </c>
-      <c r="N26" s="24">
-        <f>N14+N20</f>
-        <v/>
-      </c>
-      <c r="O26" s="24">
-        <f>O14+O20</f>
-        <v/>
-      </c>
-      <c r="P26" s="24">
-        <f>P14+P20</f>
-        <v/>
-      </c>
-      <c r="Q26" s="24">
-        <f>Q14+Q20</f>
-        <v/>
-      </c>
-      <c r="R26" s="24">
-        <f>R14+R20</f>
-        <v/>
-      </c>
-      <c r="S26" s="24">
-        <f>S14+S20</f>
-        <v/>
-      </c>
-      <c r="T26" s="24">
-        <f>T14+T20</f>
-        <v/>
-      </c>
-      <c r="U26" s="24">
-        <f>U14+U20</f>
-        <v/>
-      </c>
-      <c r="V26" s="24">
-        <f>V14+V20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="26" t="inlineStr">
-        <is>
-          <t>TOTAL DEBT SERVICE (P+I)</t>
-        </is>
-      </c>
-      <c r="C27" s="23">
-        <f>C25+C26</f>
-        <v/>
-      </c>
-      <c r="D27" s="23">
-        <f>D25+D26</f>
-        <v/>
-      </c>
-      <c r="E27" s="23">
-        <f>E25+E26</f>
-        <v/>
-      </c>
-      <c r="F27" s="23">
-        <f>F25+F26</f>
-        <v/>
-      </c>
-      <c r="G27" s="23">
-        <f>G25+G26</f>
-        <v/>
-      </c>
-      <c r="H27" s="23">
-        <f>H25+H26</f>
-        <v/>
-      </c>
-      <c r="I27" s="23">
-        <f>I25+I26</f>
-        <v/>
-      </c>
-      <c r="J27" s="23">
-        <f>J25+J26</f>
-        <v/>
-      </c>
-      <c r="K27" s="23">
-        <f>K25+K26</f>
-        <v/>
-      </c>
-      <c r="L27" s="23">
-        <f>L25+L26</f>
-        <v/>
-      </c>
-      <c r="M27" s="23">
-        <f>M25+M26</f>
-        <v/>
-      </c>
-      <c r="N27" s="23">
-        <f>N25+N26</f>
-        <v/>
-      </c>
-      <c r="O27" s="23">
-        <f>O25+O26</f>
-        <v/>
-      </c>
-      <c r="P27" s="23">
-        <f>P25+P26</f>
-        <v/>
-      </c>
-      <c r="Q27" s="23">
-        <f>Q25+Q26</f>
-        <v/>
-      </c>
-      <c r="R27" s="23">
-        <f>R25+R26</f>
-        <v/>
-      </c>
-      <c r="S27" s="23">
-        <f>S25+S26</f>
-        <v/>
-      </c>
-      <c r="T27" s="23">
-        <f>T25+T26</f>
-        <v/>
-      </c>
-      <c r="U27" s="23">
-        <f>U25+U26</f>
-        <v/>
-      </c>
-      <c r="V27" s="23">
-        <f>V25+V26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="21" t="inlineStr">
-        <is>
-          <t>EBITDA (link)</t>
-        </is>
-      </c>
-      <c r="C28" s="25">
-        <f>'Operating Budget'!C24</f>
-        <v/>
-      </c>
-      <c r="D28" s="25">
-        <f>'Operating Budget'!D24</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>'Operating Budget'!E24</f>
-        <v/>
-      </c>
-      <c r="F28" s="25">
-        <f>'Operating Budget'!F24</f>
-        <v/>
-      </c>
-      <c r="G28" s="25">
-        <f>'Operating Budget'!G24</f>
-        <v/>
-      </c>
-      <c r="H28" s="25">
-        <f>'Operating Budget'!H24</f>
-        <v/>
-      </c>
-      <c r="I28" s="25">
-        <f>'Operating Budget'!I24</f>
-        <v/>
-      </c>
-      <c r="J28" s="25">
-        <f>'Operating Budget'!J24</f>
-        <v/>
-      </c>
-      <c r="K28" s="25">
-        <f>'Operating Budget'!K24</f>
-        <v/>
-      </c>
-      <c r="L28" s="25">
-        <f>'Operating Budget'!L24</f>
-        <v/>
-      </c>
-      <c r="M28" s="25">
-        <f>'Operating Budget'!M24</f>
-        <v/>
-      </c>
-      <c r="N28" s="25">
-        <f>'Operating Budget'!N24</f>
-        <v/>
-      </c>
-      <c r="O28" s="25">
-        <f>'Operating Budget'!O24</f>
-        <v/>
-      </c>
-      <c r="P28" s="25">
-        <f>'Operating Budget'!P24</f>
-        <v/>
-      </c>
-      <c r="Q28" s="25">
-        <f>'Operating Budget'!Q24</f>
-        <v/>
-      </c>
-      <c r="R28" s="25">
-        <f>'Operating Budget'!R24</f>
-        <v/>
-      </c>
-      <c r="S28" s="25">
-        <f>'Operating Budget'!S24</f>
-        <v/>
-      </c>
-      <c r="T28" s="25">
-        <f>'Operating Budget'!T24</f>
-        <v/>
-      </c>
-      <c r="U28" s="25">
-        <f>'Operating Budget'!U24</f>
-        <v/>
-      </c>
-      <c r="V28" s="25">
-        <f>'Operating Budget'!V24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>DSCR (period)</t>
-        </is>
-      </c>
-      <c r="C29" s="57">
-        <f>IF(C27=0,0,C28/C27)</f>
-        <v/>
-      </c>
-      <c r="D29" s="57">
-        <f>IF(D27=0,0,D28/D27)</f>
-        <v/>
-      </c>
-      <c r="E29" s="57">
-        <f>IF(E27=0,0,E28/E27)</f>
-        <v/>
-      </c>
-      <c r="F29" s="57">
-        <f>IF(F27=0,0,F28/F27)</f>
-        <v/>
-      </c>
-      <c r="G29" s="57">
-        <f>IF(G27=0,0,G28/G27)</f>
-        <v/>
-      </c>
-      <c r="H29" s="57">
-        <f>IF(H27=0,0,H28/H27)</f>
-        <v/>
-      </c>
-      <c r="I29" s="57">
-        <f>IF(I27=0,0,I28/I27)</f>
-        <v/>
-      </c>
-      <c r="J29" s="57">
-        <f>IF(J27=0,0,J28/J27)</f>
-        <v/>
-      </c>
-      <c r="K29" s="57">
-        <f>IF(K27=0,0,K28/K27)</f>
-        <v/>
-      </c>
-      <c r="L29" s="57">
-        <f>IF(L27=0,0,L28/L27)</f>
-        <v/>
-      </c>
-      <c r="M29" s="57">
-        <f>IF(M27=0,0,M28/M27)</f>
-        <v/>
-      </c>
-      <c r="N29" s="57">
-        <f>IF(N27=0,0,N28/N27)</f>
-        <v/>
-      </c>
-      <c r="O29" s="57">
-        <f>IF(O27=0,0,O28/O27)</f>
-        <v/>
-      </c>
-      <c r="P29" s="57">
-        <f>IF(P27=0,0,P28/P27)</f>
-        <v/>
-      </c>
-      <c r="Q29" s="57">
-        <f>IF(Q27=0,0,Q28/Q27)</f>
-        <v/>
-      </c>
-      <c r="R29" s="57">
-        <f>IF(R27=0,0,R28/R27)</f>
-        <v/>
-      </c>
-      <c r="S29" s="57">
-        <f>IF(S27=0,0,S28/S27)</f>
-        <v/>
-      </c>
-      <c r="T29" s="57">
-        <f>IF(T27=0,0,T28/T27)</f>
-        <v/>
-      </c>
-      <c r="U29" s="57">
-        <f>IF(U27=0,0,U28/U27)</f>
-        <v/>
-      </c>
-      <c r="V29" s="57">
-        <f>IF(V27=0,0,V28/V27)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A2:V2"/>
-    <mergeCell ref="A10:V10"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="A1:V1"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="A17:V17"/>
-    <mergeCell ref="C8:N8"/>
-    <mergeCell ref="A4:V4"/>
-    <mergeCell ref="A24:V24"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>